--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -10723,7 +10723,7 @@
         <v>85330</v>
       </c>
       <c r="K64" t="n">
-        <v>26</v>
+        <v>131</v>
       </c>
     </row>
     <row r="65">
@@ -28661,7 +28661,7 @@
         <v>1239</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -7138,7 +7138,7 @@
         <v>6753</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -10723,7 +10723,7 @@
         <v>85330</v>
       </c>
       <c r="K64" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65">
@@ -28661,7 +28661,7 @@
         <v>1239</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -33019,7 +33019,7 @@
         <v>14846</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -36604,7 +36604,7 @@
         <v>2622</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -10720,10 +10720,10 @@
         <v>0.04763604126127886</v>
       </c>
       <c r="J64" t="n">
-        <v>85330</v>
+        <v>85474</v>
       </c>
       <c r="K64" t="n">
-        <v>140</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -17903,10 +17903,10 @@
         <v>1.491209836527621</v>
       </c>
       <c r="J64" t="n">
-        <v>11413</v>
+        <v>11420</v>
       </c>
       <c r="K64" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -28658,10 +28658,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3550,10 +3550,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>9726</v>
+        <v>9729</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -7135,10 +7135,10 @@
         <v>1.104437674954718</v>
       </c>
       <c r="J64" t="n">
-        <v>6753</v>
+        <v>6755</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -10720,10 +10720,10 @@
         <v>0.04763604126127886</v>
       </c>
       <c r="J64" t="n">
-        <v>85474</v>
+        <v>85491</v>
       </c>
       <c r="K64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -21488,7 +21488,7 @@
         <v>0.3333653522885549</v>
       </c>
       <c r="J64" t="n">
-        <v>6945</v>
+        <v>6946</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -33016,10 +33016,10 @@
         <v>0.3612787092903097</v>
       </c>
       <c r="J64" t="n">
-        <v>14846</v>
+        <v>14849</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -36601,10 +36601,10 @@
         <v>-0.009638181630759716</v>
       </c>
       <c r="J64" t="n">
-        <v>2622</v>
+        <v>2624</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3526,13 +3526,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>154700</v>
+        <v>163885</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.07872533296143923</v>
+        <v>0.142772470539014</v>
       </c>
       <c r="E64" t="n">
         <v>21</v>
@@ -3569,7 +3569,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.8857466063348416</v>
+        <v>-0.8921499832199408</v>
       </c>
       <c r="E65" t="n">
         <v>4</v>
@@ -10708,7 +10708,7 @@
         <v>21</v>
       </c>
       <c r="F64" t="n">
-        <v>831889</v>
+        <v>836423</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -10717,7 +10717,7 @@
         <v>4772</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.04763604126127886</v>
+        <v>0.0533133488100694</v>
       </c>
       <c r="J64" t="n">
         <v>85491</v>
@@ -10754,7 +10754,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>-0.4187311228801151</v>
+        <v>-0.4218641337620885</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3535,7 +3535,7 @@
         <v>0.142772470539014</v>
       </c>
       <c r="E64" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>6845</v>
@@ -7120,7 +7120,7 @@
         <v>0.03848362308040023</v>
       </c>
       <c r="E64" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>23472</v>
@@ -10696,16 +10696,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>927483</v>
+        <v>931175</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.03419426705782785</v>
+        <v>0.03831104896539651</v>
       </c>
       <c r="E64" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>836423</v>
@@ -10739,7 +10739,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.1949566730603149</v>
+        <v>-0.1981485757242194</v>
       </c>
       <c r="E65" t="n">
         <v>4</v>
@@ -14303,7 +14303,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -17888,7 +17888,7 @@
         <v>0.09210114851034797</v>
       </c>
       <c r="E64" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>60022</v>
@@ -21473,7 +21473,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E64" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>83286</v>
@@ -25058,7 +25058,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -28643,7 +28643,7 @@
         <v>0.01628592483419307</v>
       </c>
       <c r="E64" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -30415,7 +30415,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -33001,7 +33001,7 @@
         <v>0.2048590991331906</v>
       </c>
       <c r="E64" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>121213</v>
@@ -36586,7 +36586,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
         <v>38311</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3535,7 +3535,7 @@
         <v>0.142772470539014</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>6845</v>
@@ -7120,7 +7120,7 @@
         <v>0.03848362308040023</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>23472</v>
@@ -10696,16 +10696,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>931175</v>
+        <v>932233</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.03831104896539651</v>
+        <v>0.03949077682514939</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>836423</v>
@@ -10739,7 +10739,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.1981485757242194</v>
+        <v>-0.1990586044476005</v>
       </c>
       <c r="E65" t="n">
         <v>4</v>
@@ -14303,7 +14303,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -17888,7 +17888,7 @@
         <v>0.09210114851034797</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>60022</v>
@@ -21473,7 +21473,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>83286</v>
@@ -25058,7 +25058,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -28643,7 +28643,7 @@
         <v>0.01628592483419307</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -30415,7 +30415,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -33001,7 +33001,7 @@
         <v>0.2048590991331906</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>121213</v>
@@ -36586,7 +36586,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>38311</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3550,7 +3550,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>9729</v>
+        <v>9730</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -7135,7 +7135,7 @@
         <v>1.104437674954718</v>
       </c>
       <c r="J64" t="n">
-        <v>6755</v>
+        <v>6753</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -10720,7 +10720,7 @@
         <v>0.0533133488100694</v>
       </c>
       <c r="J64" t="n">
-        <v>85491</v>
+        <v>85492</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -33016,7 +33016,7 @@
         <v>0.3612787092903097</v>
       </c>
       <c r="J64" t="n">
-        <v>14849</v>
+        <v>14850</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -1152,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3855,23 +3855,23 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>17675</v>
+        <v>163885</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>-0.8767640004462294</v>
+        <v>0.1426609214636323</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>6845</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -3883,29 +3883,29 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>2771</v>
+        <v>9730</v>
       </c>
       <c r="K73" t="n">
-        <v>3447</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>93706</v>
+        <v>17675</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>4.301612446958981</v>
+        <v>-0.8921499832199408</v>
       </c>
       <c r="E74" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -3917,13 +3917,13 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J74" t="n">
-        <v>2370</v>
+        <v>2771</v>
       </c>
       <c r="K74" t="n">
-        <v>4406</v>
+        <v>3447</v>
       </c>
     </row>
     <row r="75">
@@ -3939,7 +3939,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0</v>
+        <v>4.301612446958981</v>
       </c>
       <c r="E75" t="n">
         <v>11</v>
@@ -3966,20 +3966,20 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>106478</v>
+        <v>93706</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.1362986361599044</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -3994,29 +3994,29 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>6592</v>
+        <v>2370</v>
       </c>
       <c r="K76" t="n">
-        <v>1</v>
+        <v>4406</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>120502</v>
+        <v>106478</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0.1317079584515111</v>
+        <v>0.1362986361599044</v>
       </c>
       <c r="E77" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -4031,29 +4031,29 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>6839</v>
+        <v>6592</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>122522</v>
+        <v>120502</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.01676320724967221</v>
+        <v>0.1317079584515111</v>
       </c>
       <c r="E78" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -4068,29 +4068,29 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>7111</v>
+        <v>6839</v>
       </c>
       <c r="K78" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>141153</v>
+        <v>122522</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.1520624867370758</v>
+        <v>0.01676320724967221</v>
       </c>
       <c r="E79" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -4105,29 +4105,29 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>8756</v>
+        <v>7111</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>143424</v>
+        <v>141153</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.0160889247837453</v>
+        <v>0.1520624867370758</v>
       </c>
       <c r="E80" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -4142,7 +4142,7 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>9265</v>
+        <v>8756</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -4151,20 +4151,20 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>92842</v>
+        <v>143424</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>-0.3526745872378402</v>
+        <v>0.0160889247837453</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -4179,29 +4179,29 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>2771</v>
+        <v>9265</v>
       </c>
       <c r="K81" t="n">
-        <v>3447</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>93706</v>
+        <v>92842</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.009306133000150794</v>
+        <v>-0.3526745872378402</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -4216,10 +4216,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>2370</v>
+        <v>2771</v>
       </c>
       <c r="K82" t="n">
-        <v>4506</v>
+        <v>3447</v>
       </c>
     </row>
     <row r="83">
@@ -4235,7 +4235,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>0.009306133000150794</v>
       </c>
       <c r="E83" t="n">
         <v>10</v>
@@ -4262,20 +4262,20 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>106833</v>
+        <v>93706</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.140087080869955</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -4290,29 +4290,29 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>6610</v>
+        <v>2370</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>4506</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>120502</v>
+        <v>106833</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.1279473570900377</v>
+        <v>0.140087080869955</v>
       </c>
       <c r="E85" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -4327,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>6862</v>
+        <v>6610</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -4336,20 +4336,20 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>122522</v>
+        <v>120502</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.01676320724967221</v>
+        <v>0.1279473570900377</v>
       </c>
       <c r="E86" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -4364,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>7152</v>
+        <v>6862</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -4373,20 +4373,20 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>141153</v>
+        <v>122522</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.1520624867370758</v>
+        <v>0.01676320724967221</v>
       </c>
       <c r="E87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -4401,7 +4401,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>8795</v>
+        <v>7152</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -4410,20 +4410,20 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>143424</v>
+        <v>141153</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.0160889247837453</v>
+        <v>0.1520624867370758</v>
       </c>
       <c r="E88" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -4438,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>9285</v>
+        <v>8795</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -4447,20 +4447,20 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>92842</v>
+        <v>143424</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-0.3526745872378402</v>
+        <v>0.0160889247837453</v>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -4475,29 +4475,29 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>2771</v>
+        <v>9285</v>
       </c>
       <c r="K89" t="n">
-        <v>3447</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>93706</v>
+        <v>92842</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.009306133000150794</v>
+        <v>-0.3526745872378402</v>
       </c>
       <c r="E90" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -4512,29 +4512,29 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>2275</v>
+        <v>2771</v>
       </c>
       <c r="K90" t="n">
-        <v>4169</v>
+        <v>3447</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>113595</v>
+        <v>93706</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.2122489488399889</v>
+        <v>0.009306133000150794</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -4549,29 +4549,29 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>6632</v>
+        <v>2275</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>4169</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>120723</v>
+        <v>113595</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.0627492407236234</v>
+        <v>0.2122489488399889</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -4586,7 +4586,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>6904</v>
+        <v>6632</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -4595,20 +4595,20 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>123393</v>
+        <v>120723</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.02211674660172461</v>
+        <v>0.0627492407236234</v>
       </c>
       <c r="E93" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -4623,7 +4623,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>7181</v>
+        <v>6904</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -4632,20 +4632,20 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>143411</v>
+        <v>123393</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.162229624046745</v>
+        <v>0.02211674660172461</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -4660,7 +4660,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>8861</v>
+        <v>7181</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -4669,59 +4669,96 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>143411</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0.162229624046745</v>
+      </c>
+      <c r="E95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>8861</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B95" t="n">
+      <c r="B96" t="n">
         <v>143478</v>
       </c>
-      <c r="C95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="3" t="n">
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
         <v>0.0004671887093737579</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E96" t="n">
         <v>10</v>
       </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" t="n">
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
         <v>9329</v>
       </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B97" s="4" t="n">
         <v>50636</v>
       </c>
-      <c r="F96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="4" t="n">
+      <c r="F97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="4" t="n">
         <v>6558</v>
       </c>
     </row>
@@ -4737,7 +4774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7440,57 +7477,57 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>54227</v>
+        <v>85003</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>-0.338953091476497</v>
+        <v>0.036217573629803</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>23472</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>27649</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>-1</v>
+        <v>1.104351047626888</v>
       </c>
       <c r="J73" t="n">
-        <v>1473</v>
+        <v>6753</v>
       </c>
       <c r="K73" t="n">
-        <v>4593</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>56849</v>
+        <v>54227</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.04835229682630424</v>
+        <v>-0.3620578097243627</v>
       </c>
       <c r="E74" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -7502,13 +7539,13 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J74" t="n">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="K74" t="n">
-        <v>4725</v>
+        <v>4593</v>
       </c>
     </row>
     <row r="75">
@@ -7524,7 +7561,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0</v>
+        <v>0.04835229682630424</v>
       </c>
       <c r="E75" t="n">
         <v>11</v>
@@ -7551,20 +7588,20 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>73144</v>
+        <v>56849</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.2866365283470246</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -7579,29 +7616,29 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>6273</v>
+        <v>1472</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>4725</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>74729</v>
+        <v>73144</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0.02166958328776113</v>
+        <v>0.2866365283470246</v>
       </c>
       <c r="E77" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -7616,7 +7653,7 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>6386</v>
+        <v>6273</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -7625,20 +7662,20 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>78663</v>
+        <v>74729</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.05264355203468533</v>
+        <v>0.02166958328776113</v>
       </c>
       <c r="E78" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -7653,29 +7690,29 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>6461</v>
+        <v>6386</v>
       </c>
       <c r="K78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>81185</v>
+        <v>78663</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.03206081639398446</v>
+        <v>0.05264355203468533</v>
       </c>
       <c r="E79" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -7690,32 +7727,32 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>6550</v>
+        <v>6461</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>83153</v>
+        <v>81185</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.02424093120650367</v>
+        <v>0.03206081639398446</v>
       </c>
       <c r="E80" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F80" t="n">
-        <v>24293</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -7727,7 +7764,7 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>6642</v>
+        <v>6550</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -7736,23 +7773,23 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>54858</v>
+        <v>83153</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>-0.340276358038796</v>
+        <v>0.02424093120650367</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>24293</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -7761,32 +7798,32 @@
         <v>0</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>1473</v>
+        <v>6642</v>
       </c>
       <c r="K81" t="n">
-        <v>4593</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>67722</v>
+        <v>54858</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.2344963359947501</v>
+        <v>-0.340276358038796</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -7798,13 +7835,13 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J82" t="n">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="K82" t="n">
-        <v>4748</v>
+        <v>4593</v>
       </c>
     </row>
     <row r="83">
@@ -7820,7 +7857,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>0.2344963359947501</v>
       </c>
       <c r="E83" t="n">
         <v>10</v>
@@ -7847,20 +7884,20 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>73144</v>
+        <v>67722</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.08006260890109565</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -7875,29 +7912,29 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>6278</v>
+        <v>1472</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>4748</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>74729</v>
+        <v>73144</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.02166958328776113</v>
+        <v>0.08006260890109565</v>
       </c>
       <c r="E85" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -7912,7 +7949,7 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>6387</v>
+        <v>6278</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -7921,20 +7958,20 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>79744</v>
+        <v>74729</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.06710915441127273</v>
+        <v>0.02166958328776113</v>
       </c>
       <c r="E86" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -7949,7 +7986,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>6477</v>
+        <v>6387</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -7958,20 +7995,20 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>81185</v>
+        <v>79744</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.01807032504012841</v>
+        <v>0.06710915441127273</v>
       </c>
       <c r="E87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -7986,7 +8023,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>6551</v>
+        <v>6477</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -7995,35 +8032,35 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>83441</v>
+        <v>81185</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.02778838455379688</v>
+        <v>0.01807032504012841</v>
       </c>
       <c r="E88" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F88" t="n">
-        <v>23761</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>8638</v>
+        <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>6657</v>
+        <v>6551</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -8032,57 +8069,57 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>54858</v>
+        <v>83441</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-0.3425534209800937</v>
+        <v>0.02778838455379688</v>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>23761</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>8638</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>1473</v>
+        <v>6657</v>
       </c>
       <c r="K89" t="n">
-        <v>4593</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>67722</v>
+        <v>54858</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.2344963359947501</v>
+        <v>-0.3425534209800937</v>
       </c>
       <c r="E90" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -8094,32 +8131,32 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J90" t="n">
-        <v>2715</v>
+        <v>1473</v>
       </c>
       <c r="K90" t="n">
-        <v>3505</v>
+        <v>4593</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>73144</v>
+        <v>67722</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.08006260890109565</v>
+        <v>0.2344963359947501</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -8134,29 +8171,29 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>6305</v>
+        <v>2715</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>3505</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>75413</v>
+        <v>73144</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.03102099967188013</v>
+        <v>0.08006260890109565</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -8171,7 +8208,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>6392</v>
+        <v>6305</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -8180,20 +8217,20 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>80213</v>
+        <v>75413</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.06364950340127033</v>
+        <v>0.03102099967188013</v>
       </c>
       <c r="E93" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -8208,7 +8245,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>6483</v>
+        <v>6392</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -8217,20 +8254,20 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>81185</v>
+        <v>80213</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.0121177365264982</v>
+        <v>0.06364950340127033</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -8245,7 +8282,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>6554</v>
+        <v>6483</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -8254,59 +8291,96 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>81185</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0.0121177365264982</v>
+      </c>
+      <c r="E95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>6554</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B95" t="n">
+      <c r="B96" t="n">
         <v>84153</v>
       </c>
-      <c r="C95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="3" t="n">
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
         <v>0.03655847755127178</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E96" t="n">
         <v>10</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F96" t="n">
         <v>23761</v>
       </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
         <v>12099</v>
       </c>
-      <c r="I95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" t="n">
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
         <v>6682</v>
       </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B97" s="4" t="n">
         <v>29295</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="F97" s="4" t="n">
         <v>23761</v>
       </c>
-      <c r="G96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="4" t="n">
+      <c r="G97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="4" t="n">
         <v>12099</v>
       </c>
-      <c r="J96" s="4" t="n">
+      <c r="J97" s="4" t="n">
         <v>5209</v>
       </c>
     </row>
@@ -8322,7 +8396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11025,60 +11099,60 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>746842</v>
+        <v>932233</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>-0.174700945371767</v>
+        <v>0.03016570250901998</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>486325</v>
+        <v>836423</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>4772</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>-0.3910959084199231</v>
+        <v>0.05321971380599958</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>85492</v>
       </c>
       <c r="K73" t="n">
-        <v>9189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>790425</v>
+        <v>746842</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.05835638595579788</v>
+        <v>-0.1988676650579844</v>
       </c>
       <c r="E74" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F74" t="n">
-        <v>642024</v>
+        <v>486325</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -11087,13 +11161,13 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.320154217858428</v>
+        <v>-0.4218641337620885</v>
       </c>
       <c r="J74" t="n">
-        <v>75457</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>10943</v>
+        <v>9189</v>
       </c>
     </row>
     <row r="75">
@@ -11109,7 +11183,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0</v>
+        <v>0.05835638595579788</v>
       </c>
       <c r="E75" t="n">
         <v>11</v>
@@ -11124,7 +11198,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0</v>
+        <v>0.320154217858428</v>
       </c>
       <c r="J75" t="n">
         <v>75457</v>
@@ -11136,23 +11210,23 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>809364</v>
+        <v>790425</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.02396052756428504</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F76" t="n">
-        <v>669090</v>
+        <v>642024</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -11161,35 +11235,35 @@
         <v>0</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.04215730253074652</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>75535</v>
+        <v>75457</v>
       </c>
       <c r="K76" t="n">
-        <v>4</v>
+        <v>10943</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>835753</v>
+        <v>809364</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0.03260461300477906</v>
+        <v>0.02396052756428504</v>
       </c>
       <c r="E77" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F77" t="n">
-        <v>726045</v>
+        <v>669090</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -11198,35 +11272,35 @@
         <v>0</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.08512307761287718</v>
+        <v>0.04215730253074652</v>
       </c>
       <c r="J77" t="n">
-        <v>77768</v>
+        <v>75535</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>854381</v>
+        <v>835753</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.02228888200221836</v>
+        <v>0.03260461300477906</v>
       </c>
       <c r="E78" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F78" t="n">
-        <v>754091</v>
+        <v>726045</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -11235,35 +11309,35 @@
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.03862845966847785</v>
+        <v>0.08512307761287718</v>
       </c>
       <c r="J78" t="n">
-        <v>78743</v>
+        <v>77768</v>
       </c>
       <c r="K78" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>878896</v>
+        <v>854381</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.02869328788912675</v>
+        <v>0.02228888200221836</v>
       </c>
       <c r="E79" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F79" t="n">
-        <v>794286</v>
+        <v>754091</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -11272,109 +11346,109 @@
         <v>0</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0.05330258549697583</v>
+        <v>0.03862845966847785</v>
       </c>
       <c r="J79" t="n">
-        <v>81702</v>
+        <v>78743</v>
       </c>
       <c r="K79" t="n">
-        <v>172</v>
+        <v>107</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>911038</v>
+        <v>878896</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.03657087983106078</v>
+        <v>0.02869328788912675</v>
       </c>
       <c r="E80" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F80" t="n">
-        <v>821903</v>
+        <v>794286</v>
       </c>
       <c r="G80" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.03482246948832033</v>
+        <v>0.05330258549697583</v>
       </c>
       <c r="J80" t="n">
-        <v>84022</v>
+        <v>81702</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>771981</v>
+        <v>911038</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>-0.1526357846763801</v>
+        <v>0.03657087983106078</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="F81" t="n">
-        <v>514576</v>
+        <v>821903</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>-0.3739532450468097</v>
+        <v>0.03482246948832033</v>
       </c>
       <c r="J81" t="n">
-        <v>47664</v>
+        <v>84022</v>
       </c>
       <c r="K81" t="n">
-        <v>24564</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>795568</v>
+        <v>771981</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.03055386078154773</v>
+        <v>-0.1526357846763801</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>645619</v>
+        <v>514576</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -11383,13 +11457,13 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.2546620907310096</v>
+        <v>-0.3739532450468097</v>
       </c>
       <c r="J82" t="n">
-        <v>73929</v>
+        <v>47664</v>
       </c>
       <c r="K82" t="n">
-        <v>172</v>
+        <v>24564</v>
       </c>
     </row>
     <row r="83">
@@ -11405,7 +11479,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>0.03055386078154773</v>
       </c>
       <c r="E83" t="n">
         <v>10</v>
@@ -11420,7 +11494,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>0.2546620907310096</v>
       </c>
       <c r="J83" t="n">
         <v>73929</v>
@@ -11432,23 +11506,23 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>813381</v>
+        <v>795568</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.02239029221889267</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F84" t="n">
-        <v>669090</v>
+        <v>645619</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -11457,35 +11531,35 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.03635425847132752</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>75698</v>
+        <v>73929</v>
       </c>
       <c r="K84" t="n">
-        <v>2</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>835753</v>
+        <v>813381</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.02750494540688804</v>
+        <v>0.02239029221889267</v>
       </c>
       <c r="E85" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F85" t="n">
-        <v>735324</v>
+        <v>669090</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -11494,35 +11568,35 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.098991167107564</v>
+        <v>0.03635425847132752</v>
       </c>
       <c r="J85" t="n">
-        <v>77868</v>
+        <v>75698</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>854381</v>
+        <v>835753</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.02228888200221836</v>
+        <v>0.02750494540688804</v>
       </c>
       <c r="E86" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F86" t="n">
-        <v>754091</v>
+        <v>735324</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -11531,35 +11605,35 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.02552208278255572</v>
+        <v>0.098991167107564</v>
       </c>
       <c r="J86" t="n">
-        <v>78935</v>
+        <v>77868</v>
       </c>
       <c r="K86" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>878896</v>
+        <v>854381</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.02869328788912675</v>
+        <v>0.02228888200221836</v>
       </c>
       <c r="E87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F87" t="n">
-        <v>794286</v>
+        <v>754091</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -11568,109 +11642,109 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.05330258549697583</v>
+        <v>0.02552208278255572</v>
       </c>
       <c r="J87" t="n">
-        <v>82128</v>
+        <v>78935</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>916483</v>
+        <v>878896</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.0427661520817025</v>
+        <v>0.02869328788912675</v>
       </c>
       <c r="E88" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F88" t="n">
-        <v>826483</v>
+        <v>794286</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>2678</v>
+        <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.04390735830670565</v>
+        <v>0.05330258549697583</v>
       </c>
       <c r="J88" t="n">
-        <v>84075</v>
+        <v>82128</v>
       </c>
       <c r="K88" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>771981</v>
+        <v>916483</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-0.157670136816504</v>
+        <v>0.0427661520817025</v>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F89" t="n">
-        <v>514576</v>
+        <v>826483</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>2678</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>-0.3794015878701483</v>
+        <v>0.04390735830670565</v>
       </c>
       <c r="J89" t="n">
-        <v>47664</v>
+        <v>84075</v>
       </c>
       <c r="K89" t="n">
-        <v>24564</v>
+        <v>130</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>795568</v>
+        <v>771981</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.03055386078154773</v>
+        <v>-0.157670136816504</v>
       </c>
       <c r="E90" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F90" t="n">
-        <v>645619</v>
+        <v>514576</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -11679,35 +11753,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.2546620907310096</v>
+        <v>-0.3794015878701483</v>
       </c>
       <c r="J90" t="n">
-        <v>73857</v>
+        <v>47664</v>
       </c>
       <c r="K90" t="n">
-        <v>45</v>
+        <v>24564</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>813381</v>
+        <v>795568</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.02239029221889267</v>
+        <v>0.03055386078154773</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F91" t="n">
-        <v>669130</v>
+        <v>645619</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -11716,35 +11790,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.03641621451661119</v>
+        <v>0.2546620907310096</v>
       </c>
       <c r="J91" t="n">
-        <v>75798</v>
+        <v>73857</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>837712</v>
+        <v>813381</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.02991341081239911</v>
+        <v>0.02239029221889267</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
-        <v>757865</v>
+        <v>669130</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -11753,10 +11827,10 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.1326124968242345</v>
+        <v>0.03641621451661119</v>
       </c>
       <c r="J92" t="n">
-        <v>77986</v>
+        <v>75798</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -11765,23 +11839,23 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>854381</v>
+        <v>837712</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.01989824665278759</v>
+        <v>0.02991341081239911</v>
       </c>
       <c r="E93" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F93" t="n">
-        <v>768568</v>
+        <v>757865</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -11790,10 +11864,10 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.01412256800353625</v>
+        <v>0.1326124968242345</v>
       </c>
       <c r="J93" t="n">
-        <v>79060</v>
+        <v>77986</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -11802,23 +11876,23 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>878954</v>
+        <v>854381</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.02876117329388177</v>
+        <v>0.01989824665278759</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F94" t="n">
-        <v>794286</v>
+        <v>768568</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -11827,10 +11901,10 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.03346223105827981</v>
+        <v>0.01412256800353625</v>
       </c>
       <c r="J94" t="n">
-        <v>82273</v>
+        <v>79060</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -11839,59 +11913,96 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>878954</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0.02876117329388177</v>
+      </c>
+      <c r="E95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" t="n">
+        <v>794286</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0.03346223105827981</v>
+      </c>
+      <c r="J95" t="n">
+        <v>82273</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B95" t="n">
+      <c r="B96" t="n">
         <v>918791</v>
       </c>
-      <c r="C95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="3" t="n">
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
         <v>0.04532319097472678</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E96" t="n">
         <v>10</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F96" t="n">
         <v>830324</v>
       </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
         <v>2839</v>
       </c>
-      <c r="I95" s="3" t="n">
+      <c r="I96" s="3" t="n">
         <v>0.0489458457029332</v>
       </c>
-      <c r="J95" t="n">
+      <c r="J96" t="n">
         <v>84310</v>
       </c>
-      <c r="K95" t="n">
+      <c r="K96" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B97" s="4" t="n">
         <v>146810</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="F97" s="4" t="n">
         <v>315748</v>
       </c>
-      <c r="G96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="4" t="n">
+      <c r="G97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="4" t="n">
         <v>2839</v>
       </c>
-      <c r="J96" s="4" t="n">
+      <c r="J97" s="4" t="n">
         <v>36646</v>
       </c>
     </row>
@@ -11920,7 +12031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -14623,20 +14734,20 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>7612</v>
+        <v>8250</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>-0.07733333333333334</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14651,16 +14762,16 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>583</v>
+        <v>675</v>
       </c>
       <c r="K73" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -14670,10 +14781,10 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0</v>
+        <v>-0.07733333333333334</v>
       </c>
       <c r="E74" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -14688,10 +14799,10 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="K74" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="75">
@@ -14734,7 +14845,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -14747,7 +14858,7 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -14762,16 +14873,16 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>668</v>
+        <v>580</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -14784,7 +14895,7 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -14799,7 +14910,7 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -14808,20 +14919,20 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>7485</v>
+        <v>7612</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>-0.01668418286915397</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -14836,7 +14947,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -14845,7 +14956,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -14855,10 +14966,10 @@
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0</v>
+        <v>-0.01668418286915397</v>
       </c>
       <c r="E79" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -14873,7 +14984,7 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -14882,20 +14993,20 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>8250</v>
+        <v>7485</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.1022044088176353</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -14910,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -14919,20 +15030,20 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>7612</v>
+        <v>8250</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>-0.07733333333333334</v>
+        <v>0.1022044088176353</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -14947,16 +15058,16 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>583</v>
+        <v>675</v>
       </c>
       <c r="K81" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -14966,10 +15077,10 @@
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0</v>
+        <v>-0.07733333333333334</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -14984,10 +15095,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="K82" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="83">
@@ -15030,7 +15141,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -15043,7 +15154,7 @@
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -15058,16 +15169,16 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>668</v>
+        <v>580</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -15080,7 +15191,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -15095,7 +15206,7 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -15104,20 +15215,20 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>7485</v>
+        <v>7612</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>-0.01668418286915397</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -15132,7 +15243,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -15141,7 +15252,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -15151,10 +15262,10 @@
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0</v>
+        <v>-0.01668418286915397</v>
       </c>
       <c r="E87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -15169,7 +15280,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -15178,20 +15289,20 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>8250</v>
+        <v>7485</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.1022044088176353</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -15206,7 +15317,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -15215,20 +15326,20 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>7612</v>
+        <v>8250</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-0.07733333333333334</v>
+        <v>0.1022044088176353</v>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -15243,16 +15354,16 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>583</v>
+        <v>675</v>
       </c>
       <c r="K89" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -15262,10 +15373,10 @@
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0</v>
+        <v>-0.07733333333333334</v>
       </c>
       <c r="E90" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -15280,16 +15391,16 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>666</v>
+        <v>583</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -15302,7 +15413,7 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -15317,7 +15428,7 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -15326,7 +15437,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -15339,7 +15450,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -15354,7 +15465,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -15363,20 +15474,20 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>7485</v>
+        <v>7612</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>-0.01668418286915397</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -15391,7 +15502,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -15400,7 +15511,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -15410,10 +15521,10 @@
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0</v>
+        <v>-0.01668418286915397</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -15428,7 +15539,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -15437,59 +15548,96 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>7485</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>674</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B95" t="n">
+      <c r="B96" t="n">
         <v>8250</v>
       </c>
-      <c r="C95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="3" t="n">
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
         <v>0.1022044088176353</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E96" t="n">
         <v>10</v>
       </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" t="n">
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
         <v>675</v>
       </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B97" s="4" t="n">
         <v>638</v>
       </c>
-      <c r="F96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="4" t="n">
+      <c r="F97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="4" t="n">
         <v>92</v>
       </c>
     </row>
@@ -15505,7 +15653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -18208,60 +18356,60 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>109032</v>
+        <v>158697</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>-0.2266850127311285</v>
+        <v>0.1255665174866837</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>15829</v>
+        <v>64520</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>81399</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>-0.7227700229434121</v>
+        <v>1.55563339580013</v>
       </c>
       <c r="J73" t="n">
-        <v>6743</v>
+        <v>11420</v>
       </c>
       <c r="K73" t="n">
-        <v>2379</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>116673</v>
+        <v>109032</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.07008034338542814</v>
+        <v>-0.3129548762736536</v>
       </c>
       <c r="E74" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F74" t="n">
-        <v>35345</v>
+        <v>15829</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -18270,13 +18418,13 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>1.232926906311201</v>
+        <v>-0.8915220087856962</v>
       </c>
       <c r="J74" t="n">
-        <v>6650</v>
+        <v>6743</v>
       </c>
       <c r="K74" t="n">
-        <v>3079</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="75">
@@ -18292,7 +18440,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0</v>
+        <v>0.07008034338542814</v>
       </c>
       <c r="E75" t="n">
         <v>11</v>
@@ -18307,7 +18455,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0</v>
+        <v>1.232926906311201</v>
       </c>
       <c r="J75" t="n">
         <v>6650</v>
@@ -18319,23 +18467,23 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>122313</v>
+        <v>116673</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.04834023295878224</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F76" t="n">
-        <v>41498</v>
+        <v>35345</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -18344,35 +18492,35 @@
         <v>0</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1740840288583958</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>9858</v>
+        <v>6650</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>127157</v>
+        <v>122313</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0.03960331281221129</v>
+        <v>0.04834023295878224</v>
       </c>
       <c r="E77" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F77" t="n">
-        <v>51337</v>
+        <v>41498</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -18381,10 +18529,10 @@
         <v>0</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.2370957636512603</v>
+        <v>0.1740840288583958</v>
       </c>
       <c r="J77" t="n">
-        <v>10115</v>
+        <v>9858</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -18393,23 +18541,23 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>127937</v>
+        <v>127157</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.006134149122738033</v>
+        <v>0.03960331281221129</v>
       </c>
       <c r="E78" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F78" t="n">
-        <v>54170</v>
+        <v>51337</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -18418,35 +18566,35 @@
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.05518436994760115</v>
+        <v>0.2370957636512603</v>
       </c>
       <c r="J78" t="n">
-        <v>10301</v>
+        <v>10115</v>
       </c>
       <c r="K78" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>140704</v>
+        <v>127937</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.09979130353220726</v>
+        <v>0.006134149122738033</v>
       </c>
       <c r="E79" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F79" t="n">
-        <v>56822</v>
+        <v>54170</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -18455,35 +18603,35 @@
         <v>0</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0.04895698726232232</v>
+        <v>0.05518436994760115</v>
       </c>
       <c r="J79" t="n">
-        <v>10692</v>
+        <v>10301</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>140993</v>
+        <v>140704</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.002053957243575165</v>
+        <v>0.09979130353220726</v>
       </c>
       <c r="E80" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F80" t="n">
-        <v>57275</v>
+        <v>56822</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -18492,10 +18640,10 @@
         <v>0</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.007972264263841469</v>
+        <v>0.04895698726232232</v>
       </c>
       <c r="J80" t="n">
-        <v>11062</v>
+        <v>10692</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -18504,23 +18652,23 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>108314</v>
+        <v>140993</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>-0.2317774641294249</v>
+        <v>0.002053957243575165</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="F81" t="n">
-        <v>15829</v>
+        <v>57275</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -18529,35 +18677,35 @@
         <v>0</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>-0.7236316019205588</v>
+        <v>0.007972264263841469</v>
       </c>
       <c r="J81" t="n">
-        <v>6741</v>
+        <v>11062</v>
       </c>
       <c r="K81" t="n">
-        <v>2829</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>118600</v>
+        <v>108314</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.09496463984341821</v>
+        <v>-0.2317774641294249</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>35345</v>
+        <v>15829</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -18566,13 +18714,13 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>1.232926906311201</v>
+        <v>-0.7236316019205588</v>
       </c>
       <c r="J82" t="n">
-        <v>6650</v>
+        <v>6741</v>
       </c>
       <c r="K82" t="n">
-        <v>3181</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="83">
@@ -18588,7 +18736,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>0.09496463984341821</v>
       </c>
       <c r="E83" t="n">
         <v>10</v>
@@ -18603,7 +18751,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>1.232926906311201</v>
       </c>
       <c r="J83" t="n">
         <v>6650</v>
@@ -18615,23 +18763,23 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>122470</v>
+        <v>118600</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.03263069139966273</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F84" t="n">
-        <v>41498</v>
+        <v>35345</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -18640,35 +18788,35 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.1740840288583958</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>9878</v>
+        <v>6650</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>3181</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>127157</v>
+        <v>122470</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.03827059688086878</v>
+        <v>0.03263069139966273</v>
       </c>
       <c r="E85" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F85" t="n">
-        <v>51337</v>
+        <v>41498</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -18677,10 +18825,10 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.2370957636512603</v>
+        <v>0.1740840288583958</v>
       </c>
       <c r="J85" t="n">
-        <v>10122</v>
+        <v>9878</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -18689,23 +18837,23 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>125374</v>
+        <v>127157</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>-0.01402203575107937</v>
+        <v>0.03827059688086878</v>
       </c>
       <c r="E86" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F86" t="n">
-        <v>56822</v>
+        <v>51337</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -18714,10 +18862,10 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.1068430177065275</v>
+        <v>0.2370957636512603</v>
       </c>
       <c r="J86" t="n">
-        <v>10331</v>
+        <v>10122</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -18726,20 +18874,20 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>140704</v>
+        <v>125374</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.1222741557260676</v>
+        <v>-0.01402203575107937</v>
       </c>
       <c r="E87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F87" t="n">
         <v>56822</v>
@@ -18751,10 +18899,10 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0</v>
+        <v>0.1068430177065275</v>
       </c>
       <c r="J87" t="n">
-        <v>10714</v>
+        <v>10331</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -18763,35 +18911,35 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>141284</v>
+        <v>140704</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.004122128724130088</v>
+        <v>0.1222741557260676</v>
       </c>
       <c r="E88" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F88" t="n">
-        <v>54804</v>
+        <v>56822</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>79817</v>
+        <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>1.369170391749674</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>11081</v>
+        <v>10714</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -18800,60 +18948,60 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>108314</v>
+        <v>141284</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-0.2333597576512556</v>
+        <v>0.004122128724130088</v>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F89" t="n">
-        <v>15829</v>
+        <v>54804</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>79817</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>-0.8824180477042958</v>
+        <v>1.369170391749674</v>
       </c>
       <c r="J89" t="n">
-        <v>6741</v>
+        <v>11081</v>
       </c>
       <c r="K89" t="n">
-        <v>2829</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>118600</v>
+        <v>108314</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.09496463984341821</v>
+        <v>-0.2333597576512556</v>
       </c>
       <c r="E90" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F90" t="n">
-        <v>35345</v>
+        <v>15829</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -18862,35 +19010,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>1.232926906311201</v>
+        <v>-0.8824180477042958</v>
       </c>
       <c r="J90" t="n">
-        <v>6394</v>
+        <v>6741</v>
       </c>
       <c r="K90" t="n">
-        <v>3232</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>122822</v>
+        <v>118600</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.03559865092748735</v>
+        <v>0.09496463984341821</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F91" t="n">
-        <v>41498</v>
+        <v>35345</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -18899,35 +19047,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.1740840288583958</v>
+        <v>1.232926906311201</v>
       </c>
       <c r="J91" t="n">
-        <v>9899</v>
+        <v>6394</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>3232</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>127169</v>
+        <v>122822</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.03539268209278468</v>
+        <v>0.03559865092748735</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
-        <v>54148</v>
+        <v>41498</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -18936,10 +19084,10 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.3048339679020676</v>
+        <v>0.1740840288583958</v>
       </c>
       <c r="J92" t="n">
-        <v>10145</v>
+        <v>9899</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -18948,23 +19096,23 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>128119</v>
+        <v>127169</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.007470374069152073</v>
+        <v>0.03539268209278468</v>
       </c>
       <c r="E93" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F93" t="n">
-        <v>56822</v>
+        <v>54148</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -18973,10 +19121,10 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.04938317204698234</v>
+        <v>0.3048339679020676</v>
       </c>
       <c r="J93" t="n">
-        <v>10390</v>
+        <v>10145</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -18985,20 +19133,20 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>140704</v>
+        <v>128119</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.0982289902356403</v>
+        <v>0.007470374069152073</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F94" t="n">
         <v>56822</v>
@@ -19010,10 +19158,10 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0</v>
+        <v>0.04938317204698234</v>
       </c>
       <c r="J94" t="n">
-        <v>10740</v>
+        <v>10390</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -19022,59 +19170,96 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>140704</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0.0982289902356403</v>
+      </c>
+      <c r="E95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" t="n">
+        <v>56822</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>10740</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B95" t="n">
+      <c r="B96" t="n">
         <v>141284</v>
       </c>
-      <c r="C95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="3" t="n">
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
         <v>0.004122128724130088</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E96" t="n">
         <v>10</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F96" t="n">
         <v>54995</v>
       </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
         <v>78744</v>
       </c>
-      <c r="I95" s="3" t="n">
+      <c r="I96" s="3" t="n">
         <v>1.353648234838619</v>
       </c>
-      <c r="J95" t="n">
+      <c r="J96" t="n">
         <v>11112</v>
       </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B97" s="4" t="n">
         <v>32970</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="F97" s="4" t="n">
         <v>39166</v>
       </c>
-      <c r="G96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="4" t="n">
+      <c r="G97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="4" t="n">
         <v>78744</v>
       </c>
-      <c r="J96" s="4" t="n">
+      <c r="J97" s="4" t="n">
         <v>4371</v>
       </c>
     </row>
@@ -19090,7 +19275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -21793,23 +21978,23 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>78930</v>
+        <v>97615</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>-0.1902206810230735</v>
+        <v>0.001477362497563378</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>46431</v>
+        <v>83286</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -21818,32 +22003,32 @@
         <v>0</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>-0.2566639450554729</v>
+        <v>0.3333653522885549</v>
       </c>
       <c r="J73" t="n">
-        <v>2434</v>
+        <v>6946</v>
       </c>
       <c r="K73" t="n">
-        <v>2430</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>79737</v>
+        <v>78930</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.01022424933485367</v>
+        <v>-0.1914152538032065</v>
       </c>
       <c r="E74" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F74" t="n">
         <v>46431</v>
@@ -21855,13 +22040,13 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0</v>
+        <v>-0.4425113464447806</v>
       </c>
       <c r="J74" t="n">
-        <v>2428</v>
+        <v>2434</v>
       </c>
       <c r="K74" t="n">
-        <v>3384</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="75">
@@ -21877,7 +22062,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0</v>
+        <v>0.01022424933485367</v>
       </c>
       <c r="E75" t="n">
         <v>11</v>
@@ -21904,23 +22089,23 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>90833</v>
+        <v>79737</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.1391574802162108</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F76" t="n">
-        <v>48866</v>
+        <v>46431</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -21929,32 +22114,32 @@
         <v>0</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.05244341065236588</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>6214</v>
+        <v>2428</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>93251</v>
+        <v>90833</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0.02662028117534376</v>
+        <v>0.1391574802162108</v>
       </c>
       <c r="E77" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F77" t="n">
         <v>48866</v>
@@ -21966,10 +22151,10 @@
         <v>0</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0</v>
+        <v>0.05244341065236588</v>
       </c>
       <c r="J77" t="n">
-        <v>6263</v>
+        <v>6214</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -21978,23 +22163,23 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>96279</v>
+        <v>93251</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.03247150164609495</v>
+        <v>0.02662028117534376</v>
       </c>
       <c r="E78" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F78" t="n">
-        <v>54278</v>
+        <v>48866</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -22003,19 +22188,19 @@
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.110751852003438</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>6346</v>
+        <v>6263</v>
       </c>
       <c r="K78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -22025,13 +22210,13 @@
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0</v>
+        <v>0.03247150164609495</v>
       </c>
       <c r="E79" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F79" t="n">
-        <v>58545</v>
+        <v>54278</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -22040,35 +22225,35 @@
         <v>0</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0.07861380301411253</v>
+        <v>0.110751852003438</v>
       </c>
       <c r="J79" t="n">
-        <v>6431</v>
+        <v>6346</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>97471</v>
+        <v>96279</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.0123806853000135</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F80" t="n">
-        <v>68960</v>
+        <v>58545</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -22077,10 +22262,10 @@
         <v>0</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.1778973439234777</v>
+        <v>0.07861380301411253</v>
       </c>
       <c r="J80" t="n">
-        <v>6853</v>
+        <v>6431</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -22089,23 +22274,23 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>79737</v>
+        <v>97471</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>-0.1819412953596454</v>
+        <v>0.0123806853000135</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="F81" t="n">
-        <v>46431</v>
+        <v>68960</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -22114,19 +22299,19 @@
         <v>0</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>-0.3266966357308584</v>
+        <v>0.1778973439234777</v>
       </c>
       <c r="J81" t="n">
-        <v>2434</v>
+        <v>6853</v>
       </c>
       <c r="K81" t="n">
-        <v>3079</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -22136,10 +22321,10 @@
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0</v>
+        <v>-0.1819412953596454</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>46431</v>
@@ -22151,13 +22336,13 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0</v>
+        <v>-0.3266966357308584</v>
       </c>
       <c r="J82" t="n">
-        <v>2428</v>
+        <v>2434</v>
       </c>
       <c r="K82" t="n">
-        <v>3395</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="83">
@@ -22200,23 +22385,23 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>90982</v>
+        <v>79737</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.1410261233806138</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F84" t="n">
-        <v>48866</v>
+        <v>46431</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -22225,32 +22410,32 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.05244341065236588</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>6216</v>
+        <v>2428</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>3395</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>93251</v>
+        <v>90982</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.02493899892286386</v>
+        <v>0.1410261233806138</v>
       </c>
       <c r="E85" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F85" t="n">
         <v>48866</v>
@@ -22262,10 +22447,10 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0</v>
+        <v>0.05244341065236588</v>
       </c>
       <c r="J85" t="n">
-        <v>6266</v>
+        <v>6216</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -22274,23 +22459,23 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>96279</v>
+        <v>93251</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.03247150164609495</v>
+        <v>0.02493899892286386</v>
       </c>
       <c r="E86" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F86" t="n">
-        <v>54278</v>
+        <v>48866</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -22299,10 +22484,10 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.110751852003438</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>6351</v>
+        <v>6266</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -22311,7 +22496,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -22321,13 +22506,13 @@
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0</v>
+        <v>0.03247150164609495</v>
       </c>
       <c r="E87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F87" t="n">
-        <v>58545</v>
+        <v>54278</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -22336,10 +22521,10 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.07861380301411253</v>
+        <v>0.110751852003438</v>
       </c>
       <c r="J87" t="n">
-        <v>6435</v>
+        <v>6351</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -22348,23 +22533,23 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>97615</v>
+        <v>96279</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.01387633855773325</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F88" t="n">
-        <v>83286</v>
+        <v>58545</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -22373,10 +22558,10 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.422598001537279</v>
+        <v>0.07861380301411253</v>
       </c>
       <c r="J88" t="n">
-        <v>6869</v>
+        <v>6435</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -22385,23 +22570,23 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>79737</v>
+        <v>97615</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-0.1831480817497311</v>
+        <v>0.01387633855773325</v>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F89" t="n">
-        <v>46431</v>
+        <v>83286</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -22410,32 +22595,32 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>-0.4425113464447806</v>
+        <v>0.422598001537279</v>
       </c>
       <c r="J89" t="n">
-        <v>2434</v>
+        <v>6869</v>
       </c>
       <c r="K89" t="n">
-        <v>3079</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>87942</v>
+        <v>79737</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.1029007863350766</v>
+        <v>-0.1831480817497311</v>
       </c>
       <c r="E90" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F90" t="n">
         <v>46431</v>
@@ -22447,35 +22632,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0</v>
+        <v>-0.4425113464447806</v>
       </c>
       <c r="J90" t="n">
-        <v>2359</v>
+        <v>2434</v>
       </c>
       <c r="K90" t="n">
-        <v>3430</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>90982</v>
+        <v>87942</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.03456823815696709</v>
+        <v>0.1029007863350766</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F91" t="n">
-        <v>48866</v>
+        <v>46431</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -22484,35 +22669,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.05244341065236588</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>6221</v>
+        <v>2359</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>93726</v>
+        <v>90982</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.03015981183091161</v>
+        <v>0.03456823815696709</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
-        <v>50607</v>
+        <v>48866</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -22521,10 +22706,10 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.03562804403879998</v>
+        <v>0.05244341065236588</v>
       </c>
       <c r="J92" t="n">
-        <v>6271</v>
+        <v>6221</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -22533,20 +22718,20 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>96279</v>
+        <v>93726</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.02723897317713335</v>
+        <v>0.03015981183091161</v>
       </c>
       <c r="E93" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F93" t="n">
         <v>50607</v>
@@ -22558,10 +22743,10 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0</v>
+        <v>0.03562804403879998</v>
       </c>
       <c r="J93" t="n">
-        <v>6357</v>
+        <v>6271</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -22570,7 +22755,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -22580,13 +22765,13 @@
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0</v>
+        <v>0.02723897317713335</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F94" t="n">
-        <v>58545</v>
+        <v>50607</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -22595,10 +22780,10 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.1568557709407789</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>6447</v>
+        <v>6357</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -22607,59 +22792,96 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>96279</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" t="n">
+        <v>58545</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0.1568557709407789</v>
+      </c>
+      <c r="J95" t="n">
+        <v>6447</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B95" t="n">
+      <c r="B96" t="n">
         <v>97615</v>
       </c>
-      <c r="C95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="3" t="n">
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
         <v>0.01387633855773325</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E96" t="n">
         <v>10</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F96" t="n">
         <v>83286</v>
       </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="3" t="n">
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
         <v>0.422598001537279</v>
       </c>
-      <c r="J95" t="n">
+      <c r="J96" t="n">
         <v>6879</v>
       </c>
-      <c r="K95" t="n">
+      <c r="K96" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B97" s="4" t="n">
         <v>17878</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="F97" s="4" t="n">
         <v>36855</v>
       </c>
-      <c r="G96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="4" t="n">
+      <c r="G97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="4" t="n">
         <v>4445</v>
       </c>
     </row>
@@ -22675,7 +22897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -25378,20 +25600,20 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>6139</v>
+        <v>6136</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.0004889178617992178</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -25406,16 +25628,16 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>551</v>
+        <v>587</v>
       </c>
       <c r="K73" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -25425,10 +25647,10 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0</v>
+        <v>0.0004889178617992178</v>
       </c>
       <c r="E74" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -25489,20 +25711,20 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>6138</v>
+        <v>6139</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>-0.0001628929793125916</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -25517,29 +25739,29 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>583</v>
+        <v>551</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>6158</v>
+        <v>6138</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0.003258390355164549</v>
+        <v>-0.0001628929793125916</v>
       </c>
       <c r="E77" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -25563,20 +25785,20 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>6136</v>
+        <v>6158</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>-0.003572588502760637</v>
+        <v>0.003258390355164549</v>
       </c>
       <c r="E78" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -25600,7 +25822,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -25610,10 +25832,10 @@
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0</v>
+        <v>-0.003572588502760637</v>
       </c>
       <c r="E79" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -25637,7 +25859,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -25650,7 +25872,7 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -25665,7 +25887,7 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -25674,20 +25896,20 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>6139</v>
+        <v>6136</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>0.0004889178617992178</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -25702,16 +25924,16 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>551</v>
+        <v>585</v>
       </c>
       <c r="K81" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -25721,10 +25943,10 @@
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0</v>
+        <v>0.0004889178617992178</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -25742,7 +25964,7 @@
         <v>551</v>
       </c>
       <c r="K82" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="83">
@@ -25785,20 +26007,20 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>6138</v>
+        <v>6139</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>-0.0001628929793125916</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -25813,29 +26035,29 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>583</v>
+        <v>551</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>6158</v>
+        <v>6138</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.003258390355164549</v>
+        <v>-0.0001628929793125916</v>
       </c>
       <c r="E85" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -25859,20 +26081,20 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>6136</v>
+        <v>6158</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>-0.003572588502760637</v>
+        <v>0.003258390355164549</v>
       </c>
       <c r="E86" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -25896,7 +26118,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -25906,10 +26128,10 @@
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0</v>
+        <v>-0.003572588502760637</v>
       </c>
       <c r="E87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -25933,7 +26155,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -25946,7 +26168,7 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -25961,7 +26183,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -25970,20 +26192,20 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>6139</v>
+        <v>6136</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.0004889178617992178</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -25998,16 +26220,16 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>551</v>
+        <v>586</v>
       </c>
       <c r="K89" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -26017,10 +26239,10 @@
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0</v>
+        <v>0.0004889178617992178</v>
       </c>
       <c r="E90" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -26038,26 +26260,26 @@
         <v>551</v>
       </c>
       <c r="K90" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>6138</v>
+        <v>6139</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>-0.0001628929793125916</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -26072,29 +26294,29 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>583</v>
+        <v>551</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>6158</v>
+        <v>6138</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.003258390355164549</v>
+        <v>-0.0001628929793125916</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -26118,20 +26340,20 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>6136</v>
+        <v>6158</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>-0.003572588502760637</v>
+        <v>0.003258390355164549</v>
       </c>
       <c r="E93" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -26155,7 +26377,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -26165,10 +26387,10 @@
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0</v>
+        <v>-0.003572588502760637</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -26192,7 +26414,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -26205,46 +26427,83 @@
         <v>0</v>
       </c>
       <c r="E95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>583</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>6136</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
         <v>10</v>
       </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" t="n">
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
         <v>586</v>
       </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B97" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="F96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="4" t="n">
+      <c r="F97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="4" t="n">
         <v>35</v>
       </c>
     </row>
@@ -26260,7 +26519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -28963,20 +29222,20 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>23142</v>
+        <v>27582</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>-0.1528972509974743</v>
+        <v>0.009626999524140707</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -28991,29 +29250,29 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>975</v>
+        <v>1243</v>
       </c>
       <c r="K73" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>58808</v>
+        <v>23142</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>1.541180537550773</v>
+        <v>-0.1609745486186643</v>
       </c>
       <c r="E74" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -29028,10 +29287,10 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>657</v>
+        <v>975</v>
       </c>
       <c r="K74" t="n">
-        <v>532</v>
+        <v>103</v>
       </c>
     </row>
     <row r="75">
@@ -29047,7 +29306,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0</v>
+        <v>1.541180537550773</v>
       </c>
       <c r="E75" t="n">
         <v>11</v>
@@ -29074,20 +29333,20 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>26385</v>
+        <v>58808</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>-0.5513365528499524</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -29102,16 +29361,16 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>1176</v>
+        <v>657</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>532</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -29121,10 +29380,10 @@
         <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0</v>
+        <v>-0.5513365528499524</v>
       </c>
       <c r="E77" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -29139,7 +29398,7 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>1192</v>
+        <v>1176</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -29148,20 +29407,20 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>26336</v>
+        <v>26385</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>-0.001857115785484177</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -29176,7 +29435,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>1200</v>
+        <v>1192</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -29185,20 +29444,20 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>26385</v>
+        <v>26336</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.001860571081409478</v>
+        <v>-0.001857115785484177</v>
       </c>
       <c r="E79" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -29213,7 +29472,7 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>1212</v>
+        <v>1200</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -29222,20 +29481,20 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>27319</v>
+        <v>26385</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.03539890089065757</v>
+        <v>0.001860571081409478</v>
       </c>
       <c r="E80" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -29250,7 +29509,7 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>1232</v>
+        <v>1212</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -29259,20 +29518,20 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>23142</v>
+        <v>27319</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>-0.1528972509974743</v>
+        <v>0.03539890089065757</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -29287,29 +29546,29 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>975</v>
+        <v>1232</v>
       </c>
       <c r="K81" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>58808</v>
+        <v>23142</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>1.541180537550773</v>
+        <v>-0.1528972509974743</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -29324,10 +29583,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>657</v>
+        <v>975</v>
       </c>
       <c r="K82" t="n">
-        <v>534</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83">
@@ -29343,7 +29602,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>1.541180537550773</v>
       </c>
       <c r="E83" t="n">
         <v>10</v>
@@ -29370,20 +29629,20 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>26385</v>
+        <v>58808</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>-0.5513365528499524</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -29398,16 +29657,16 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>1178</v>
+        <v>657</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>534</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -29417,10 +29676,10 @@
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0</v>
+        <v>-0.5513365528499524</v>
       </c>
       <c r="E85" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -29435,7 +29694,7 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>1193</v>
+        <v>1178</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -29444,20 +29703,20 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>26336</v>
+        <v>26385</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>-0.001857115785484177</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -29472,29 +29731,29 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>1200</v>
+        <v>1193</v>
       </c>
       <c r="K86" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>26385</v>
+        <v>26336</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.001860571081409478</v>
+        <v>-0.001857115785484177</v>
       </c>
       <c r="E87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -29509,29 +29768,29 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>1212</v>
+        <v>1200</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27319</v>
+        <v>26385</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.03539890089065757</v>
+        <v>0.001860571081409478</v>
       </c>
       <c r="E88" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -29546,7 +29805,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>1233</v>
+        <v>1212</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -29555,20 +29814,20 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>23142</v>
+        <v>27319</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-0.1528972509974743</v>
+        <v>0.03539890089065757</v>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -29583,29 +29842,29 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>975</v>
+        <v>1233</v>
       </c>
       <c r="K89" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>58808</v>
+        <v>23142</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>1.541180537550773</v>
+        <v>-0.1528972509974743</v>
       </c>
       <c r="E90" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -29620,29 +29879,29 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>606</v>
+        <v>975</v>
       </c>
       <c r="K90" t="n">
-        <v>550</v>
+        <v>103</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>26385</v>
+        <v>58808</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>-0.5513365528499524</v>
+        <v>1.541180537550773</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -29657,16 +29916,16 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>1179</v>
+        <v>606</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -29676,10 +29935,10 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>-0.5513365528499524</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -29694,7 +29953,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>1194</v>
+        <v>1179</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -29703,20 +29962,20 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>26336</v>
+        <v>26385</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>-0.001857115785484177</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -29731,7 +29990,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>1204</v>
+        <v>1194</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -29740,20 +29999,20 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>26385</v>
+        <v>26336</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.001860571081409478</v>
+        <v>-0.001857115785484177</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -29768,7 +30027,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>1215</v>
+        <v>1204</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -29777,59 +30036,96 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>26385</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0.001860571081409478</v>
+      </c>
+      <c r="E95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1215</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B95" t="n">
+      <c r="B96" t="n">
         <v>27319</v>
       </c>
-      <c r="C95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="3" t="n">
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
         <v>0.03539890089065757</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E96" t="n">
         <v>10</v>
       </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" t="n">
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
         <v>1233</v>
       </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B97" s="4" t="n">
         <v>4177</v>
       </c>
-      <c r="F96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="4" t="n">
+      <c r="F97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="4" t="n">
         <v>258</v>
       </c>
     </row>
@@ -29845,7 +30141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -30476,7 +30772,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -30489,7 +30785,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -30504,7 +30800,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -30513,7 +30809,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -30526,7 +30822,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -30550,7 +30846,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -30563,7 +30859,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -30585,24 +30881,61 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>11103</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>289</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="4" t="n">
+      <c r="B21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30618,7 +30951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -33321,60 +33654,60 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>99162</v>
+        <v>203773</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>-0.4319121876324805</v>
+        <v>0.1673923255840599</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>52380</v>
+        <v>121213</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>1298</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>-0.4179805993533118</v>
+        <v>0.3612787092903097</v>
       </c>
       <c r="J73" t="n">
-        <v>5061</v>
+        <v>14850</v>
       </c>
       <c r="K73" t="n">
-        <v>3147</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>125484</v>
+        <v>99162</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.2654444242754281</v>
+        <v>-0.5133702698591079</v>
       </c>
       <c r="E74" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F74" t="n">
-        <v>84583</v>
+        <v>52380</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -33383,13 +33716,13 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.6147957235586101</v>
+        <v>-0.5724465558194775</v>
       </c>
       <c r="J74" t="n">
-        <v>6286</v>
+        <v>5061</v>
       </c>
       <c r="K74" t="n">
-        <v>4237</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="75">
@@ -33405,7 +33738,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0</v>
+        <v>0.2654444242754281</v>
       </c>
       <c r="E75" t="n">
         <v>11</v>
@@ -33420,7 +33753,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0</v>
+        <v>0.6147957235586101</v>
       </c>
       <c r="J75" t="n">
         <v>6286</v>
@@ -33432,23 +33765,23 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>143125</v>
+        <v>125484</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.1405836600682159</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F76" t="n">
-        <v>83216</v>
+        <v>84583</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -33457,35 +33790,35 @@
         <v>0</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>-0.0161616400458721</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>10720</v>
+        <v>6286</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>149441</v>
+        <v>143125</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0.0441292576419214</v>
+        <v>0.1405836600682159</v>
       </c>
       <c r="E77" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F77" t="n">
-        <v>86719</v>
+        <v>83216</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -33494,10 +33827,10 @@
         <v>0</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.04209527014035763</v>
+        <v>-0.0161616400458721</v>
       </c>
       <c r="J77" t="n">
-        <v>11000</v>
+        <v>10720</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -33506,23 +33839,23 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>150177</v>
+        <v>149441</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.004925020576682437</v>
+        <v>0.0441292576419214</v>
       </c>
       <c r="E78" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F78" t="n">
-        <v>86528</v>
+        <v>86719</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -33531,35 +33864,35 @@
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>-0.002202516172926348</v>
+        <v>0.04209527014035763</v>
       </c>
       <c r="J78" t="n">
-        <v>11265</v>
+        <v>11000</v>
       </c>
       <c r="K78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>159088</v>
+        <v>150177</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.05933664942035066</v>
+        <v>0.004925020576682437</v>
       </c>
       <c r="E79" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F79" t="n">
-        <v>88126</v>
+        <v>86528</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -33568,35 +33901,35 @@
         <v>0</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0.01846801035502959</v>
+        <v>-0.002202516172926348</v>
       </c>
       <c r="J79" t="n">
-        <v>12893</v>
+        <v>11265</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>174849</v>
+        <v>159088</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.09907095444030976</v>
+        <v>0.05933664942035066</v>
       </c>
       <c r="E80" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F80" t="n">
-        <v>90151</v>
+        <v>88126</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -33605,10 +33938,10 @@
         <v>0</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.02297846265574291</v>
+        <v>0.01846801035502959</v>
       </c>
       <c r="J80" t="n">
-        <v>13804</v>
+        <v>12893</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -33617,23 +33950,23 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>125484</v>
+        <v>174849</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>-0.2823293241597035</v>
+        <v>0.09907095444030976</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="F81" t="n">
-        <v>77628</v>
+        <v>90151</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -33642,19 +33975,19 @@
         <v>0</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>-0.1389113820146199</v>
+        <v>0.02297846265574291</v>
       </c>
       <c r="J81" t="n">
-        <v>5023</v>
+        <v>13804</v>
       </c>
       <c r="K81" t="n">
-        <v>3876</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -33664,13 +33997,13 @@
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0</v>
+        <v>-0.2823293241597035</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>84583</v>
+        <v>77628</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -33679,13 +34012,13 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.08959396094192817</v>
+        <v>-0.1389113820146199</v>
       </c>
       <c r="J82" t="n">
-        <v>6286</v>
+        <v>5023</v>
       </c>
       <c r="K82" t="n">
-        <v>4246</v>
+        <v>3876</v>
       </c>
     </row>
     <row r="83">
@@ -33716,7 +34049,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>0.08959396094192817</v>
       </c>
       <c r="J83" t="n">
         <v>6286</v>
@@ -33728,23 +34061,23 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>143125</v>
+        <v>125484</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.1405836600682159</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F84" t="n">
-        <v>83216</v>
+        <v>84583</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -33753,35 +34086,35 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>-0.0161616400458721</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>10750</v>
+        <v>6286</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>4246</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>149441</v>
+        <v>143125</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.0441292576419214</v>
+        <v>0.1405836600682159</v>
       </c>
       <c r="E85" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F85" t="n">
-        <v>86719</v>
+        <v>83216</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -33790,10 +34123,10 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.04209527014035763</v>
+        <v>-0.0161616400458721</v>
       </c>
       <c r="J85" t="n">
-        <v>11020</v>
+        <v>10750</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -33802,23 +34135,23 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>150177</v>
+        <v>149441</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.004925020576682437</v>
+        <v>0.0441292576419214</v>
       </c>
       <c r="E86" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F86" t="n">
-        <v>86528</v>
+        <v>86719</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -33827,10 +34160,10 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>-0.002202516172926348</v>
+        <v>0.04209527014035763</v>
       </c>
       <c r="J86" t="n">
-        <v>11272</v>
+        <v>11020</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -33839,23 +34172,23 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>159088</v>
+        <v>150177</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.05933664942035066</v>
+        <v>0.004925020576682437</v>
       </c>
       <c r="E87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F87" t="n">
-        <v>88126</v>
+        <v>86528</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -33864,10 +34197,10 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.01846801035502959</v>
+        <v>-0.002202516172926348</v>
       </c>
       <c r="J87" t="n">
-        <v>12901</v>
+        <v>11272</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -33876,35 +34209,35 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>174849</v>
+        <v>159088</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.09907095444030976</v>
+        <v>0.05933664942035066</v>
       </c>
       <c r="E88" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F88" t="n">
-        <v>105046</v>
+        <v>88126</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>1088</v>
+        <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.2043437804961079</v>
+        <v>0.01846801035502959</v>
       </c>
       <c r="J88" t="n">
-        <v>14383</v>
+        <v>12901</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -33913,60 +34246,60 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>125484</v>
+        <v>174849</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-0.2823293241597035</v>
+        <v>0.09907095444030976</v>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F89" t="n">
-        <v>77628</v>
+        <v>105046</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>1088</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>-0.2685849963253999</v>
+        <v>0.2043437804961079</v>
       </c>
       <c r="J89" t="n">
-        <v>5023</v>
+        <v>14383</v>
       </c>
       <c r="K89" t="n">
-        <v>3876</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>36793</v>
+        <v>125484</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.7067913040706385</v>
+        <v>-0.2823293241597035</v>
       </c>
       <c r="E90" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F90" t="n">
-        <v>84583</v>
+        <v>77628</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -33975,35 +34308,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.08959396094192817</v>
+        <v>-0.2685849963253999</v>
       </c>
       <c r="J90" t="n">
-        <v>4963</v>
+        <v>5023</v>
       </c>
       <c r="K90" t="n">
-        <v>5534</v>
+        <v>3876</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>143125</v>
+        <v>36793</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>2.890006251189085</v>
+        <v>-0.7067913040706385</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F91" t="n">
-        <v>83216</v>
+        <v>84583</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -34012,35 +34345,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-0.0161616400458721</v>
+        <v>0.08959396094192817</v>
       </c>
       <c r="J91" t="n">
-        <v>10755</v>
+        <v>4963</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>5534</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>149787</v>
+        <v>143125</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.04654672489082969</v>
+        <v>2.890006251189085</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
-        <v>86719</v>
+        <v>83216</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -34049,10 +34382,10 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.04209527014035763</v>
+        <v>-0.0161616400458721</v>
       </c>
       <c r="J92" t="n">
-        <v>11032</v>
+        <v>10755</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -34061,23 +34394,23 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>150177</v>
+        <v>149787</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.002603697250095135</v>
+        <v>0.04654672489082969</v>
       </c>
       <c r="E93" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F93" t="n">
-        <v>78736</v>
+        <v>86719</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -34086,10 +34419,10 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>-0.0920559508296913</v>
+        <v>0.04209527014035763</v>
       </c>
       <c r="J93" t="n">
-        <v>11322</v>
+        <v>11032</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -34098,23 +34431,23 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>159088</v>
+        <v>150177</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.05933664942035066</v>
+        <v>0.002603697250095135</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F94" t="n">
-        <v>88126</v>
+        <v>78736</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -34123,10 +34456,10 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.1192592968908758</v>
+        <v>-0.0920559508296913</v>
       </c>
       <c r="J94" t="n">
-        <v>12961</v>
+        <v>11322</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -34135,59 +34468,96 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>159088</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0.05933664942035066</v>
+      </c>
+      <c r="E95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" t="n">
+        <v>88126</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0.1192592968908758</v>
+      </c>
+      <c r="J95" t="n">
+        <v>12961</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B95" t="n">
+      <c r="B96" t="n">
         <v>174892</v>
       </c>
-      <c r="C95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="3" t="n">
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
         <v>0.09934124509705321</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E96" t="n">
         <v>10</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F96" t="n">
         <v>105046</v>
       </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
         <v>1088</v>
       </c>
-      <c r="I95" s="3" t="n">
+      <c r="I96" s="3" t="n">
         <v>0.2043437804961079</v>
       </c>
-      <c r="J95" t="n">
+      <c r="J96" t="n">
         <v>14610</v>
       </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B97" s="4" t="n">
         <v>49408</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="F97" s="4" t="n">
         <v>27418</v>
       </c>
-      <c r="G96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="4" t="n">
+      <c r="G97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="4" t="n">
         <v>1088</v>
       </c>
-      <c r="J96" s="4" t="n">
+      <c r="J97" s="4" t="n">
         <v>9587</v>
       </c>
     </row>
@@ -34203,7 +34573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -36906,60 +37276,60 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2026</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>31523</v>
+        <v>39551</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>-0.2029784329094081</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>31603</v>
+        <v>38311</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>-0.185573652200804</v>
+        <v>-0.009638181630759716</v>
       </c>
       <c r="J73" t="n">
-        <v>1051</v>
+        <v>2624</v>
       </c>
       <c r="K73" t="n">
-        <v>1062</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>31413</v>
+        <v>31523</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.003489515591790122</v>
+        <v>-0.2029784329094081</v>
       </c>
       <c r="E74" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F74" t="n">
-        <v>33248</v>
+        <v>31603</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -36968,13 +37338,13 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.05205202037781223</v>
+        <v>-0.177647671090294</v>
       </c>
       <c r="J74" t="n">
-        <v>1178</v>
+        <v>1051</v>
       </c>
       <c r="K74" t="n">
-        <v>1045</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="75">
@@ -36990,7 +37360,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0</v>
+        <v>-0.003489515591790122</v>
       </c>
       <c r="E75" t="n">
         <v>11</v>
@@ -37005,7 +37375,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0</v>
+        <v>0.05205202037781223</v>
       </c>
       <c r="J75" t="n">
         <v>1178</v>
@@ -37017,23 +37387,23 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>37455</v>
+        <v>31413</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.1923407506446376</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F76" t="n">
-        <v>25871</v>
+        <v>33248</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -37042,35 +37412,35 @@
         <v>0</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>-0.2218780076997112</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>2246</v>
+        <v>1178</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>37759</v>
+        <v>37455</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0.008116406354291816</v>
+        <v>0.1923407506446376</v>
       </c>
       <c r="E77" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F77" t="n">
-        <v>33725</v>
+        <v>25871</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -37079,10 +37449,10 @@
         <v>0</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.3035831626145105</v>
+        <v>-0.2218780076997112</v>
       </c>
       <c r="J77" t="n">
-        <v>2305</v>
+        <v>2246</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -37091,23 +37461,23 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>37867</v>
+        <v>37759</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.002860245239545539</v>
+        <v>0.008116406354291816</v>
       </c>
       <c r="E78" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F78" t="n">
-        <v>37621</v>
+        <v>33725</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -37116,35 +37486,35 @@
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.115522609340252</v>
+        <v>0.3035831626145105</v>
       </c>
       <c r="J78" t="n">
-        <v>2376</v>
+        <v>2305</v>
       </c>
       <c r="K78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>38957</v>
+        <v>37867</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.02878495787889191</v>
+        <v>0.002860245239545539</v>
       </c>
       <c r="E79" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F79" t="n">
-        <v>38804</v>
+        <v>37621</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -37153,35 +37523,35 @@
         <v>0</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0.03144520347678158</v>
+        <v>0.115522609340252</v>
       </c>
       <c r="J79" t="n">
-        <v>2511</v>
+        <v>2376</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>39551</v>
+        <v>38957</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.01524758066586236</v>
+        <v>0.02878495787889191</v>
       </c>
       <c r="E80" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F80" t="n">
-        <v>38889</v>
+        <v>38804</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -37190,10 +37560,10 @@
         <v>0</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.002190495825172663</v>
+        <v>0.03144520347678158</v>
       </c>
       <c r="J80" t="n">
-        <v>2583</v>
+        <v>2511</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -37202,23 +37572,23 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>31413</v>
+        <v>39551</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>-0.2057596520947637</v>
+        <v>0.01524758066586236</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="F81" t="n">
-        <v>28900</v>
+        <v>38889</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -37227,35 +37597,35 @@
         <v>0</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>-0.2568592661163825</v>
+        <v>0.002190495825172663</v>
       </c>
       <c r="J81" t="n">
-        <v>1051</v>
+        <v>2583</v>
       </c>
       <c r="K81" t="n">
-        <v>1107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>36790</v>
+        <v>31413</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.1711711711711712</v>
+        <v>-0.2057596520947637</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>33248</v>
+        <v>28900</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -37264,13 +37634,13 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.1504498269896194</v>
+        <v>-0.2568592661163825</v>
       </c>
       <c r="J82" t="n">
-        <v>1178</v>
+        <v>1051</v>
       </c>
       <c r="K82" t="n">
-        <v>1048</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="83">
@@ -37286,7 +37656,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>0.1711711711711712</v>
       </c>
       <c r="E83" t="n">
         <v>10</v>
@@ -37301,7 +37671,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>0.1504498269896194</v>
       </c>
       <c r="J83" t="n">
         <v>1178</v>
@@ -37313,23 +37683,23 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>37455</v>
+        <v>36790</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.01807556401195977</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F84" t="n">
-        <v>25871</v>
+        <v>33248</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -37338,35 +37708,35 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>-0.2218780076997112</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>2245</v>
+        <v>1178</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>37759</v>
+        <v>37455</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.008116406354291816</v>
+        <v>0.01807556401195977</v>
       </c>
       <c r="E85" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F85" t="n">
-        <v>35299</v>
+        <v>25871</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -37375,10 +37745,10 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.3644234857562522</v>
+        <v>-0.2218780076997112</v>
       </c>
       <c r="J85" t="n">
-        <v>2322</v>
+        <v>2245</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -37387,23 +37757,23 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>37867</v>
+        <v>37759</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.002860245239545539</v>
+        <v>0.008116406354291816</v>
       </c>
       <c r="E86" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F86" t="n">
-        <v>37621</v>
+        <v>35299</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -37412,35 +37782,35 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.06578090030879062</v>
+        <v>0.3644234857562522</v>
       </c>
       <c r="J86" t="n">
-        <v>2380</v>
+        <v>2322</v>
       </c>
       <c r="K86" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>38957</v>
+        <v>37867</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.02878495787889191</v>
+        <v>0.002860245239545539</v>
       </c>
       <c r="E87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F87" t="n">
-        <v>38804</v>
+        <v>37621</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -37449,109 +37819,109 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.03144520347678158</v>
+        <v>0.06578090030879062</v>
       </c>
       <c r="J87" t="n">
-        <v>2521</v>
+        <v>2380</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>39551</v>
+        <v>38957</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.01524758066586236</v>
+        <v>0.02878495787889191</v>
       </c>
       <c r="E88" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F88" t="n">
-        <v>38771</v>
+        <v>38804</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.002216266364292341</v>
+        <v>0.03144520347678158</v>
       </c>
       <c r="J88" t="n">
-        <v>2583</v>
+        <v>2521</v>
       </c>
       <c r="K88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>31413</v>
+        <v>39551</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-0.2057596520947637</v>
+        <v>0.01524758066586236</v>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F89" t="n">
-        <v>28900</v>
+        <v>38771</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>-0.2568783749035742</v>
+        <v>0.002216266364292341</v>
       </c>
       <c r="J89" t="n">
-        <v>1051</v>
+        <v>2583</v>
       </c>
       <c r="K89" t="n">
-        <v>1107</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>36790</v>
+        <v>31413</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.1711711711711712</v>
+        <v>-0.2057596520947637</v>
       </c>
       <c r="E90" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F90" t="n">
-        <v>33248</v>
+        <v>28900</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -37560,35 +37930,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.1504498269896194</v>
+        <v>-0.2568783749035742</v>
       </c>
       <c r="J90" t="n">
-        <v>2196</v>
+        <v>1051</v>
       </c>
       <c r="K90" t="n">
-        <v>5</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>37455</v>
+        <v>36790</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.01807556401195977</v>
+        <v>0.1711711711711712</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F91" t="n">
-        <v>25871</v>
+        <v>33248</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -37597,35 +37967,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-0.2218780076997112</v>
+        <v>0.1504498269896194</v>
       </c>
       <c r="J91" t="n">
-        <v>2254</v>
+        <v>2196</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>37759</v>
+        <v>37455</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.008116406354291816</v>
+        <v>0.01807556401195977</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
-        <v>35299</v>
+        <v>25871</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -37634,10 +38004,10 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.3644234857562522</v>
+        <v>-0.2218780076997112</v>
       </c>
       <c r="J92" t="n">
-        <v>2324</v>
+        <v>2254</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -37646,23 +38016,23 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>38247</v>
+        <v>37759</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.01292407108239095</v>
+        <v>0.008116406354291816</v>
       </c>
       <c r="E93" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F93" t="n">
-        <v>37621</v>
+        <v>35299</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -37671,10 +38041,10 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.06578090030879062</v>
+        <v>0.3644234857562522</v>
       </c>
       <c r="J93" t="n">
-        <v>2395</v>
+        <v>2324</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -37683,23 +38053,23 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>38957</v>
+        <v>38247</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.01856354746777525</v>
+        <v>0.01292407108239095</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F94" t="n">
-        <v>38804</v>
+        <v>37621</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -37708,10 +38078,10 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.03144520347678158</v>
+        <v>0.06578090030879062</v>
       </c>
       <c r="J94" t="n">
-        <v>2525</v>
+        <v>2395</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -37720,59 +38090,96 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>38957</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0.01856354746777525</v>
+      </c>
+      <c r="E95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" t="n">
+        <v>38804</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0.03144520347678158</v>
+      </c>
+      <c r="J95" t="n">
+        <v>2525</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B95" t="n">
+      <c r="B96" t="n">
         <v>39551</v>
       </c>
-      <c r="C95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="3" t="n">
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
         <v>0.01524758066586236</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E96" t="n">
         <v>10</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F96" t="n">
         <v>38825</v>
       </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
         <v>119</v>
       </c>
-      <c r="I95" s="3" t="n">
+      <c r="I96" s="3" t="n">
         <v>0.003607875476754974</v>
       </c>
-      <c r="J95" t="n">
+      <c r="J96" t="n">
         <v>2585</v>
       </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B97" s="4" t="n">
         <v>8138</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="F97" s="4" t="n">
         <v>9925</v>
       </c>
-      <c r="G96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="4" t="n">
+      <c r="G97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="4" t="n">
         <v>119</v>
       </c>
-      <c r="J96" s="4" t="n">
+      <c r="J97" s="4" t="n">
         <v>1534</v>
       </c>
     </row>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -11103,13 +11103,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>932233</v>
+        <v>935287</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.03016570250901998</v>
+        <v>0.03354053053534232</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -11146,7 +11146,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.1988676650579844</v>
+        <v>-0.2014836087746328</v>
       </c>
       <c r="E74" t="n">
         <v>7</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3868,7 +3868,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>6845</v>
@@ -7490,7 +7490,7 @@
         <v>0.036217573629803</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>23472</v>
@@ -11112,7 +11112,7 @@
         <v>0.03354053053534232</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>836423</v>
@@ -14747,7 +14747,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18369,7 +18369,7 @@
         <v>0.1255665174866837</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>64520</v>
@@ -21991,7 +21991,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>83286</v>
@@ -25613,7 +25613,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29235,7 +29235,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -30785,7 +30785,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -33667,7 +33667,7 @@
         <v>0.1673923255840599</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>121213</v>
@@ -37289,7 +37289,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>38311</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3886,7 +3886,7 @@
         <v>9730</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -22009,7 +22009,7 @@
         <v>6946</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3871,7 +3871,7 @@
         <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>6845</v>
+        <v>7346</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -11115,7 +11115,7 @@
         <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>836423</v>
+        <v>837438</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -11124,10 +11124,10 @@
         <v>4772</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.05321971380599958</v>
+        <v>0.05449054638288495</v>
       </c>
       <c r="J73" t="n">
-        <v>85492</v>
+        <v>85499</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -11161,7 +11161,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>-0.4218641337620885</v>
+        <v>-0.4225608814903646</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -33685,7 +33685,7 @@
         <v>14850</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3871,7 +3871,7 @@
         <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>7346</v>
+        <v>8739</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -11127,7 +11127,7 @@
         <v>0.05449054638288495</v>
       </c>
       <c r="J73" t="n">
-        <v>85499</v>
+        <v>85504</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -33682,10 +33682,10 @@
         <v>0.3612787092903097</v>
       </c>
       <c r="J73" t="n">
-        <v>14850</v>
+        <v>14853</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3868,7 +3868,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>8739</v>
@@ -3883,10 +3883,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>9730</v>
+        <v>9731</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -7490,7 +7490,7 @@
         <v>0.036217573629803</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>23472</v>
@@ -11103,16 +11103,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>935287</v>
+        <v>936197</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.03354053053534232</v>
+        <v>0.03454612762242592</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>837438</v>
@@ -11127,7 +11127,7 @@
         <v>0.05449054638288495</v>
       </c>
       <c r="J73" t="n">
-        <v>85504</v>
+        <v>85510</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -11146,7 +11146,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.2014836087746328</v>
+        <v>-0.2022597807939996</v>
       </c>
       <c r="E74" t="n">
         <v>7</v>
@@ -14747,7 +14747,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18369,7 +18369,7 @@
         <v>0.1255665174866837</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>64520</v>
@@ -18384,7 +18384,7 @@
         <v>1.55563339580013</v>
       </c>
       <c r="J73" t="n">
-        <v>11420</v>
+        <v>11426</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -21991,7 +21991,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>83286</v>
@@ -22006,10 +22006,10 @@
         <v>0.3333653522885549</v>
       </c>
       <c r="J73" t="n">
-        <v>6946</v>
+        <v>6947</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -25613,7 +25613,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29235,7 +29235,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -30785,7 +30785,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -33667,7 +33667,7 @@
         <v>0.1673923255840599</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>121213</v>
@@ -33682,7 +33682,7 @@
         <v>0.3612787092903097</v>
       </c>
       <c r="J73" t="n">
-        <v>14853</v>
+        <v>14858</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -37289,7 +37289,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>38311</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -11127,7 +11127,7 @@
         <v>0.05449054638288495</v>
       </c>
       <c r="J73" t="n">
-        <v>85510</v>
+        <v>85517</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -18384,7 +18384,7 @@
         <v>1.55563339580013</v>
       </c>
       <c r="J73" t="n">
-        <v>11426</v>
+        <v>11430</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -33682,7 +33682,7 @@
         <v>0.3612787092903097</v>
       </c>
       <c r="J73" t="n">
-        <v>14858</v>
+        <v>14861</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -7508,7 +7508,7 @@
         <v>6753</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -11130,7 +11130,7 @@
         <v>85517</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -18387,7 +18387,7 @@
         <v>11430</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74">
@@ -33685,7 +33685,7 @@
         <v>14861</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3886,7 +3886,7 @@
         <v>9731</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
     </row>
     <row r="74">
@@ -11130,7 +11130,7 @@
         <v>85517</v>
       </c>
       <c r="K73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -18387,7 +18387,7 @@
         <v>11430</v>
       </c>
       <c r="K73" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74">
@@ -33685,7 +33685,7 @@
         <v>14861</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3868,7 +3868,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>8739</v>
@@ -3883,10 +3883,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>9731</v>
+        <v>10032</v>
       </c>
       <c r="K73" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -7490,7 +7490,7 @@
         <v>0.036217573629803</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>23472</v>
@@ -7505,10 +7505,10 @@
         <v>1.104351047626888</v>
       </c>
       <c r="J73" t="n">
-        <v>6753</v>
+        <v>6754</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -11112,7 +11112,7 @@
         <v>0.03454612762242592</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>837438</v>
@@ -11130,7 +11130,7 @@
         <v>85517</v>
       </c>
       <c r="K73" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74">
@@ -14747,7 +14747,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18369,7 +18369,7 @@
         <v>0.1255665174866837</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>64520</v>
@@ -18384,10 +18384,10 @@
         <v>1.55563339580013</v>
       </c>
       <c r="J73" t="n">
-        <v>11430</v>
+        <v>11453</v>
       </c>
       <c r="K73" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -21991,7 +21991,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>83286</v>
@@ -25613,7 +25613,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29235,7 +29235,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -30785,7 +30785,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -33667,7 +33667,7 @@
         <v>0.1673923255840599</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>121213</v>
@@ -33682,10 +33682,10 @@
         <v>0.3612787092903097</v>
       </c>
       <c r="J73" t="n">
-        <v>14861</v>
+        <v>14866</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -37289,7 +37289,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>38311</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3868,7 +3868,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>8739</v>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>10032</v>
+        <v>10033</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -7490,7 +7490,7 @@
         <v>0.036217573629803</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>23472</v>
@@ -7508,7 +7508,7 @@
         <v>6754</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -11112,7 +11112,7 @@
         <v>0.03454612762242592</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>837438</v>
@@ -11127,10 +11127,10 @@
         <v>0.05449054638288495</v>
       </c>
       <c r="J73" t="n">
-        <v>85517</v>
+        <v>85532</v>
       </c>
       <c r="K73" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -14747,7 +14747,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18369,7 +18369,7 @@
         <v>0.1255665174866837</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>64520</v>
@@ -18387,7 +18387,7 @@
         <v>11453</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -21991,7 +21991,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>83286</v>
@@ -25613,7 +25613,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29235,7 +29235,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -30785,7 +30785,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -33667,7 +33667,7 @@
         <v>0.1673923255840599</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>121213</v>
@@ -33685,7 +33685,7 @@
         <v>14866</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -37289,7 +37289,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>38311</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3868,7 +3868,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>8739</v>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>10033</v>
+        <v>10035</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -7490,7 +7490,7 @@
         <v>0.036217573629803</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>23472</v>
@@ -7508,7 +7508,7 @@
         <v>6754</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -11112,7 +11112,7 @@
         <v>0.03454612762242592</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>837438</v>
@@ -11130,7 +11130,7 @@
         <v>85532</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -14747,7 +14747,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18369,7 +18369,7 @@
         <v>0.1255665174866837</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>64520</v>
@@ -18384,10 +18384,10 @@
         <v>1.55563339580013</v>
       </c>
       <c r="J73" t="n">
-        <v>11453</v>
+        <v>11457</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -21991,7 +21991,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>83286</v>
@@ -25613,7 +25613,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -25631,7 +25631,7 @@
         <v>587</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -29235,7 +29235,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -30785,7 +30785,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -33658,16 +33658,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>203773</v>
+        <v>203909</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.1673923255840599</v>
+        <v>0.1681714541058927</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>121213</v>
@@ -33682,10 +33682,10 @@
         <v>0.3612787092903097</v>
       </c>
       <c r="J73" t="n">
-        <v>14866</v>
+        <v>14869</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -33701,7 +33701,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.5133702698591079</v>
+        <v>-0.5136948344604702</v>
       </c>
       <c r="E74" t="n">
         <v>7</v>
@@ -37289,7 +37289,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>38311</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3868,7 +3868,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>8739</v>
@@ -3886,7 +3886,7 @@
         <v>10035</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -7490,7 +7490,7 @@
         <v>0.036217573629803</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>23472</v>
@@ -7508,7 +7508,7 @@
         <v>6754</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -11103,16 +11103,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>936197</v>
+        <v>936408</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.03454612762242592</v>
+        <v>0.03477929354042003</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>837438</v>
@@ -11130,7 +11130,7 @@
         <v>85532</v>
       </c>
       <c r="K73" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74">
@@ -11146,7 +11146,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.2022597807939996</v>
+        <v>-0.202439534903589</v>
       </c>
       <c r="E74" t="n">
         <v>7</v>
@@ -14747,7 +14747,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18369,7 +18369,7 @@
         <v>0.1255665174866837</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>64520</v>
@@ -18387,7 +18387,7 @@
         <v>11457</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -21991,7 +21991,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>83286</v>
@@ -25613,7 +25613,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29235,7 +29235,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -30785,7 +30785,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -33667,7 +33667,7 @@
         <v>0.1681714541058927</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>121213</v>
@@ -33685,7 +33685,7 @@
         <v>14869</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -37289,7 +37289,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>38311</v>
@@ -37307,7 +37307,7 @@
         <v>2624</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3868,7 +3868,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>8739</v>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>10035</v>
+        <v>10051</v>
       </c>
       <c r="K73" t="n">
         <v>1</v>
@@ -7490,7 +7490,7 @@
         <v>0.036217573629803</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>23472</v>
@@ -7505,10 +7505,10 @@
         <v>1.104351047626888</v>
       </c>
       <c r="J73" t="n">
-        <v>6754</v>
+        <v>6760</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -11112,22 +11112,22 @@
         <v>0.03477929354042003</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
-        <v>837438</v>
+        <v>838386</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>4772</v>
+        <v>4798</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.05449054638288495</v>
+        <v>0.05571004483597496</v>
       </c>
       <c r="J73" t="n">
-        <v>85532</v>
+        <v>85570</v>
       </c>
       <c r="K73" t="n">
         <v>19</v>
@@ -11161,7 +11161,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>-0.4225608814903646</v>
+        <v>-0.4232279075504279</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -14747,7 +14747,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18360,16 +18360,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>158697</v>
+        <v>163890</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.1255665174866837</v>
+        <v>0.1623981332406573</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>64520</v>
@@ -18384,10 +18384,10 @@
         <v>1.55563339580013</v>
       </c>
       <c r="J73" t="n">
-        <v>11457</v>
+        <v>11461</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -18403,7 +18403,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.3129548762736536</v>
+        <v>-0.3347245103423028</v>
       </c>
       <c r="E74" t="n">
         <v>7</v>
@@ -21991,7 +21991,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>83286</v>
@@ -22009,7 +22009,7 @@
         <v>6947</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -25613,7 +25613,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -25628,10 +25628,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -29235,7 +29235,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -30785,7 +30785,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -33667,7 +33667,7 @@
         <v>0.1681714541058927</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>121213</v>
@@ -33682,7 +33682,7 @@
         <v>0.3612787092903097</v>
       </c>
       <c r="J73" t="n">
-        <v>14869</v>
+        <v>14874</v>
       </c>
       <c r="K73" t="n">
         <v>2</v>
@@ -37289,7 +37289,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>38311</v>
@@ -37304,10 +37304,10 @@
         <v>-0.009638181630759716</v>
       </c>
       <c r="J73" t="n">
-        <v>2624</v>
+        <v>2627</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3886,7 +3886,7 @@
         <v>10051</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -11130,7 +11130,7 @@
         <v>85570</v>
       </c>
       <c r="K73" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="74">
@@ -18387,7 +18387,7 @@
         <v>11461</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3883,10 +3883,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>10051</v>
+        <v>10055</v>
       </c>
       <c r="K73" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -7505,10 +7505,10 @@
         <v>1.104351047626888</v>
       </c>
       <c r="J73" t="n">
-        <v>6760</v>
+        <v>6761</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -11127,10 +11127,10 @@
         <v>0.05571004483597496</v>
       </c>
       <c r="J73" t="n">
-        <v>85570</v>
+        <v>85622</v>
       </c>
       <c r="K73" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -18384,10 +18384,10 @@
         <v>1.55563339580013</v>
       </c>
       <c r="J73" t="n">
-        <v>11461</v>
+        <v>11467</v>
       </c>
       <c r="K73" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -33682,10 +33682,10 @@
         <v>0.3612787092903097</v>
       </c>
       <c r="J73" t="n">
-        <v>14874</v>
+        <v>14876</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -11130,7 +11130,7 @@
         <v>85622</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74">
@@ -18372,16 +18372,16 @@
         <v>9</v>
       </c>
       <c r="F73" t="n">
-        <v>64520</v>
+        <v>65216</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>81399</v>
+        <v>81414</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>1.55563339580013</v>
+        <v>1.568085888925863</v>
       </c>
       <c r="J73" t="n">
         <v>11467</v>
@@ -18418,7 +18418,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>-0.8915220087856962</v>
+        <v>-0.8920480120030008</v>
       </c>
       <c r="J74" t="n">
         <v>6743</v>
@@ -22009,7 +22009,7 @@
         <v>6947</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -33685,7 +33685,7 @@
         <v>14876</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -37307,7 +37307,7 @@
         <v>2627</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3868,7 +3868,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>8739</v>
@@ -7490,7 +7490,7 @@
         <v>0.036217573629803</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>23472</v>
@@ -11112,7 +11112,7 @@
         <v>0.03477929354042003</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>838386</v>
@@ -11127,10 +11127,10 @@
         <v>0.05571004483597496</v>
       </c>
       <c r="J73" t="n">
-        <v>85622</v>
+        <v>85638</v>
       </c>
       <c r="K73" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -14747,7 +14747,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18369,7 +18369,7 @@
         <v>0.1623981332406573</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>65216</v>
@@ -21991,7 +21991,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>83286</v>
@@ -22009,7 +22009,7 @@
         <v>6947</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -25613,7 +25613,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29235,7 +29235,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -30785,7 +30785,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -33667,7 +33667,7 @@
         <v>0.1681714541058927</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>121213</v>
@@ -33685,7 +33685,7 @@
         <v>14876</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -37289,7 +37289,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>38311</v>
@@ -37307,7 +37307,7 @@
         <v>2627</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3868,7 +3868,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>8739</v>
@@ -7490,7 +7490,7 @@
         <v>0.036217573629803</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>23472</v>
@@ -11112,7 +11112,7 @@
         <v>0.03477929354042003</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>838386</v>
@@ -11130,7 +11130,7 @@
         <v>85638</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -14747,7 +14747,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18360,16 +18360,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>163890</v>
+        <v>164288</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.1623981332406573</v>
+        <v>0.1652209684168718</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>65216</v>
@@ -18403,7 +18403,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.3347245103423028</v>
+        <v>-0.3363361901051811</v>
       </c>
       <c r="E74" t="n">
         <v>7</v>
@@ -21991,7 +21991,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>83286</v>
@@ -22009,7 +22009,7 @@
         <v>6947</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -25613,7 +25613,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29235,7 +29235,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -30785,7 +30785,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -33667,7 +33667,7 @@
         <v>0.1681714541058927</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>121213</v>
@@ -33685,7 +33685,7 @@
         <v>14876</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -37289,7 +37289,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>38311</v>
@@ -37307,7 +37307,7 @@
         <v>2627</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3868,7 +3868,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F73" t="n">
         <v>8739</v>
@@ -3883,10 +3883,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>10055</v>
+        <v>10056</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -7490,7 +7490,7 @@
         <v>0.036217573629803</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F73" t="n">
         <v>23472</v>
@@ -11112,7 +11112,7 @@
         <v>0.03477929354042003</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F73" t="n">
         <v>838386</v>
@@ -11127,10 +11127,10 @@
         <v>0.05571004483597496</v>
       </c>
       <c r="J73" t="n">
-        <v>85638</v>
+        <v>85645</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -14747,7 +14747,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18369,7 +18369,7 @@
         <v>0.1652209684168718</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F73" t="n">
         <v>65216</v>
@@ -21991,7 +21991,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F73" t="n">
         <v>83286</v>
@@ -22006,10 +22006,10 @@
         <v>0.3333653522885549</v>
       </c>
       <c r="J73" t="n">
-        <v>6947</v>
+        <v>6953</v>
       </c>
       <c r="K73" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -25613,7 +25613,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29235,7 +29235,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -30785,7 +30785,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -33667,7 +33667,7 @@
         <v>0.1681714541058927</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F73" t="n">
         <v>121213</v>
@@ -33682,10 +33682,10 @@
         <v>0.3612787092903097</v>
       </c>
       <c r="J73" t="n">
-        <v>14876</v>
+        <v>14879</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -37280,16 +37280,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>39551</v>
+        <v>40606</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0</v>
+        <v>0.02667442036863796</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F73" t="n">
         <v>38311</v>
@@ -37304,10 +37304,10 @@
         <v>-0.009638181630759716</v>
       </c>
       <c r="J73" t="n">
-        <v>2627</v>
+        <v>2632</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -37323,7 +37323,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.2029784329094081</v>
+        <v>-0.2236861547554549</v>
       </c>
       <c r="E74" t="n">
         <v>7</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3868,7 +3868,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E73" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F73" t="n">
         <v>8739</v>
@@ -7490,7 +7490,7 @@
         <v>0.036217573629803</v>
       </c>
       <c r="E73" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F73" t="n">
         <v>23472</v>
@@ -11112,19 +11112,19 @@
         <v>0.03477929354042003</v>
       </c>
       <c r="E73" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F73" t="n">
-        <v>838386</v>
+        <v>839541</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>4798</v>
+        <v>4804</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.05571004483597496</v>
+        <v>0.05716367697564383</v>
       </c>
       <c r="J73" t="n">
         <v>85645</v>
@@ -11161,7 +11161,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>-0.4232279075504279</v>
+        <v>-0.4240209866819842</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -14747,7 +14747,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18369,7 +18369,7 @@
         <v>0.1652209684168718</v>
       </c>
       <c r="E73" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F73" t="n">
         <v>65216</v>
@@ -21991,7 +21991,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E73" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F73" t="n">
         <v>83286</v>
@@ -25613,7 +25613,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29235,7 +29235,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E73" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -30785,7 +30785,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -33667,7 +33667,7 @@
         <v>0.1681714541058927</v>
       </c>
       <c r="E73" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F73" t="n">
         <v>121213</v>
@@ -37289,7 +37289,7 @@
         <v>0.02667442036863796</v>
       </c>
       <c r="E73" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F73" t="n">
         <v>38311</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3868,7 +3868,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E73" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>8739</v>
@@ -7490,7 +7490,7 @@
         <v>0.036217573629803</v>
       </c>
       <c r="E73" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>23472</v>
@@ -7499,10 +7499,10 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>27649</v>
+        <v>47173</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>1.104351047626888</v>
+        <v>1.908039352900012</v>
       </c>
       <c r="J73" t="n">
         <v>6761</v>
@@ -11112,7 +11112,7 @@
         <v>0.03477929354042003</v>
       </c>
       <c r="E73" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>839541</v>
@@ -14747,7 +14747,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18369,7 +18369,7 @@
         <v>0.1652209684168718</v>
       </c>
       <c r="E73" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>65216</v>
@@ -21991,7 +21991,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E73" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>83286</v>
@@ -25613,7 +25613,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29235,7 +29235,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E73" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -30785,7 +30785,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -33667,7 +33667,7 @@
         <v>0.1681714541058927</v>
       </c>
       <c r="E73" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>121213</v>
@@ -37289,7 +37289,7 @@
         <v>0.02667442036863796</v>
       </c>
       <c r="E73" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
         <v>38311</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -1152,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3868,7 +3868,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E73" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F73" t="n">
         <v>8739</v>
@@ -4188,23 +4188,23 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>92842</v>
+        <v>163885</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.3526745872378402</v>
+        <v>0.1426609214636323</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>8739</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -4216,29 +4216,29 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>2771</v>
+        <v>10056</v>
       </c>
       <c r="K82" t="n">
-        <v>3447</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>93706</v>
+        <v>92842</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.009306133000150794</v>
+        <v>-0.4334929981389389</v>
       </c>
       <c r="E83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -4250,13 +4250,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J83" t="n">
-        <v>2370</v>
+        <v>2771</v>
       </c>
       <c r="K83" t="n">
-        <v>4506</v>
+        <v>3447</v>
       </c>
     </row>
     <row r="84">
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.009306133000150794</v>
       </c>
       <c r="E84" t="n">
         <v>10</v>
@@ -4299,20 +4299,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>106833</v>
+        <v>93706</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.140087080869955</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -4327,29 +4327,29 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>6610</v>
+        <v>2370</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>4506</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>120502</v>
+        <v>106833</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.1279473570900377</v>
+        <v>0.140087080869955</v>
       </c>
       <c r="E86" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -4364,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>6862</v>
+        <v>6610</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -4373,20 +4373,20 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>122522</v>
+        <v>120502</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.01676320724967221</v>
+        <v>0.1279473570900377</v>
       </c>
       <c r="E87" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -4401,7 +4401,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>7152</v>
+        <v>6862</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -4410,20 +4410,20 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>141153</v>
+        <v>122522</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.1520624867370758</v>
+        <v>0.01676320724967221</v>
       </c>
       <c r="E88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -4438,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>8795</v>
+        <v>7152</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -4447,20 +4447,20 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>143424</v>
+        <v>141153</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.0160889247837453</v>
+        <v>0.1520624867370758</v>
       </c>
       <c r="E89" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -4475,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>9285</v>
+        <v>8795</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -4484,20 +4484,20 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>92842</v>
+        <v>143424</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.3526745872378402</v>
+        <v>0.0160889247837453</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -4512,29 +4512,29 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>2771</v>
+        <v>9285</v>
       </c>
       <c r="K90" t="n">
-        <v>3447</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>93706</v>
+        <v>92842</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.009306133000150794</v>
+        <v>-0.3526745872378402</v>
       </c>
       <c r="E91" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -4549,29 +4549,29 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>2275</v>
+        <v>2771</v>
       </c>
       <c r="K91" t="n">
-        <v>4169</v>
+        <v>3447</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>113595</v>
+        <v>93706</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.2122489488399889</v>
+        <v>0.009306133000150794</v>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -4586,29 +4586,29 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>6632</v>
+        <v>2275</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>4169</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>120723</v>
+        <v>113595</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.0627492407236234</v>
+        <v>0.2122489488399889</v>
       </c>
       <c r="E93" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -4623,7 +4623,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>6904</v>
+        <v>6632</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -4632,20 +4632,20 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>123393</v>
+        <v>120723</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.02211674660172461</v>
+        <v>0.0627492407236234</v>
       </c>
       <c r="E94" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -4660,7 +4660,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>7181</v>
+        <v>6904</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -4669,20 +4669,20 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>143411</v>
+        <v>123393</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.162229624046745</v>
+        <v>0.02211674660172461</v>
       </c>
       <c r="E95" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -4697,7 +4697,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>8861</v>
+        <v>7181</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -4706,59 +4706,96 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>143411</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.162229624046745</v>
+      </c>
+      <c r="E96" t="n">
+        <v>4</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>8861</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>143478</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.0004671887093737579</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>10</v>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
         <v>9329</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>50636</v>
       </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>6558</v>
       </c>
     </row>
@@ -4774,7 +4811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7490,7 +7527,7 @@
         <v>0.036217573629803</v>
       </c>
       <c r="E73" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F73" t="n">
         <v>23472</v>
@@ -7810,57 +7847,57 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>54858</v>
+        <v>85003</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.340276358038796</v>
+        <v>0.02224814498574916</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>23472</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>47173</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-1</v>
+        <v>1.908039352900012</v>
       </c>
       <c r="J82" t="n">
-        <v>1473</v>
+        <v>6763</v>
       </c>
       <c r="K82" t="n">
-        <v>4593</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>67722</v>
+        <v>54858</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.2344963359947501</v>
+        <v>-0.3546345423102714</v>
       </c>
       <c r="E83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -7872,13 +7909,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J83" t="n">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="K83" t="n">
-        <v>4748</v>
+        <v>4593</v>
       </c>
     </row>
     <row r="84">
@@ -7894,7 +7931,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.2344963359947501</v>
       </c>
       <c r="E84" t="n">
         <v>10</v>
@@ -7921,20 +7958,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>73144</v>
+        <v>67722</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.08006260890109565</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -7949,29 +7986,29 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>6278</v>
+        <v>1472</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>4748</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>74729</v>
+        <v>73144</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.02166958328776113</v>
+        <v>0.08006260890109565</v>
       </c>
       <c r="E86" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -7986,7 +8023,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>6387</v>
+        <v>6278</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -7995,20 +8032,20 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>79744</v>
+        <v>74729</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.06710915441127273</v>
+        <v>0.02166958328776113</v>
       </c>
       <c r="E87" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -8023,7 +8060,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>6477</v>
+        <v>6387</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -8032,20 +8069,20 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>81185</v>
+        <v>79744</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.01807032504012841</v>
+        <v>0.06710915441127273</v>
       </c>
       <c r="E88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -8060,7 +8097,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>6551</v>
+        <v>6477</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -8069,35 +8106,35 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>83441</v>
+        <v>81185</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.02778838455379688</v>
+        <v>0.01807032504012841</v>
       </c>
       <c r="E89" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F89" t="n">
-        <v>23761</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>8638</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>6657</v>
+        <v>6551</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -8106,57 +8143,57 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>54858</v>
+        <v>83441</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.3425534209800937</v>
+        <v>0.02778838455379688</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>23761</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>8638</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>1473</v>
+        <v>6657</v>
       </c>
       <c r="K90" t="n">
-        <v>4593</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>67722</v>
+        <v>54858</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.2344963359947501</v>
+        <v>-0.3425534209800937</v>
       </c>
       <c r="E91" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -8168,32 +8205,32 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J91" t="n">
-        <v>2715</v>
+        <v>1473</v>
       </c>
       <c r="K91" t="n">
-        <v>3505</v>
+        <v>4593</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>73144</v>
+        <v>67722</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.08006260890109565</v>
+        <v>0.2344963359947501</v>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -8208,29 +8245,29 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>6305</v>
+        <v>2715</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>3505</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>75413</v>
+        <v>73144</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.03102099967188013</v>
+        <v>0.08006260890109565</v>
       </c>
       <c r="E93" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -8245,7 +8282,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>6392</v>
+        <v>6305</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -8254,20 +8291,20 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>80213</v>
+        <v>75413</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.06364950340127033</v>
+        <v>0.03102099967188013</v>
       </c>
       <c r="E94" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -8282,7 +8319,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>6483</v>
+        <v>6392</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -8291,20 +8328,20 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>81185</v>
+        <v>80213</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.0121177365264982</v>
+        <v>0.06364950340127033</v>
       </c>
       <c r="E95" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -8319,7 +8356,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>6554</v>
+        <v>6483</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -8328,59 +8365,96 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>81185</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.0121177365264982</v>
+      </c>
+      <c r="E96" t="n">
+        <v>4</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>6554</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>84153</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.03655847755127178</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>10</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>23761</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>12099</v>
       </c>
-      <c r="I96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
         <v>6682</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>29295</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>23761</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>12099</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>5209</v>
       </c>
     </row>
@@ -8396,7 +8470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11112,7 +11186,7 @@
         <v>0.03477929354042003</v>
       </c>
       <c r="E73" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F73" t="n">
         <v>839541</v>
@@ -11432,60 +11506,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>771981</v>
+        <v>936408</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.1526357846763801</v>
+        <v>0.02784735653178023</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>514576</v>
+        <v>839541</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>4804</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.3739532450468097</v>
+        <v>0.0272524317320502</v>
       </c>
       <c r="J82" t="n">
-        <v>47664</v>
+        <v>85644</v>
       </c>
       <c r="K82" t="n">
-        <v>24564</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>795568</v>
+        <v>771981</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.03055386078154773</v>
+        <v>-0.1755933311120793</v>
       </c>
       <c r="E83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>645619</v>
+        <v>514576</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -11494,13 +11568,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.2546620907310096</v>
+        <v>-0.3905619148570786</v>
       </c>
       <c r="J83" t="n">
-        <v>73929</v>
+        <v>47664</v>
       </c>
       <c r="K83" t="n">
-        <v>172</v>
+        <v>24564</v>
       </c>
     </row>
     <row r="84">
@@ -11516,7 +11590,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.03055386078154773</v>
       </c>
       <c r="E84" t="n">
         <v>10</v>
@@ -11531,7 +11605,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>0.2546620907310096</v>
       </c>
       <c r="J84" t="n">
         <v>73929</v>
@@ -11543,23 +11617,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>813381</v>
+        <v>795568</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.02239029221889267</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F85" t="n">
-        <v>669090</v>
+        <v>645619</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -11568,35 +11642,35 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.03635425847132752</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>75698</v>
+        <v>73929</v>
       </c>
       <c r="K85" t="n">
-        <v>2</v>
+        <v>172</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>835753</v>
+        <v>813381</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.02750494540688804</v>
+        <v>0.02239029221889267</v>
       </c>
       <c r="E86" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F86" t="n">
-        <v>735324</v>
+        <v>669090</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -11605,35 +11679,35 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.098991167107564</v>
+        <v>0.03635425847132752</v>
       </c>
       <c r="J86" t="n">
-        <v>77868</v>
+        <v>75698</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>854381</v>
+        <v>835753</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.02228888200221836</v>
+        <v>0.02750494540688804</v>
       </c>
       <c r="E87" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F87" t="n">
-        <v>754091</v>
+        <v>735324</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -11642,35 +11716,35 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.02552208278255572</v>
+        <v>0.098991167107564</v>
       </c>
       <c r="J87" t="n">
-        <v>78935</v>
+        <v>77868</v>
       </c>
       <c r="K87" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>878896</v>
+        <v>854381</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.02869328788912675</v>
+        <v>0.02228888200221836</v>
       </c>
       <c r="E88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F88" t="n">
-        <v>794286</v>
+        <v>754091</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -11679,109 +11753,109 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.05330258549697583</v>
+        <v>0.02552208278255572</v>
       </c>
       <c r="J88" t="n">
-        <v>82128</v>
+        <v>78935</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>916483</v>
+        <v>878896</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.0427661520817025</v>
+        <v>0.02869328788912675</v>
       </c>
       <c r="E89" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F89" t="n">
-        <v>826483</v>
+        <v>794286</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>2678</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.04390735830670565</v>
+        <v>0.05330258549697583</v>
       </c>
       <c r="J89" t="n">
-        <v>84075</v>
+        <v>82128</v>
       </c>
       <c r="K89" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>771981</v>
+        <v>916483</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.157670136816504</v>
+        <v>0.0427661520817025</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F90" t="n">
-        <v>514576</v>
+        <v>826483</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>2678</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.3794015878701483</v>
+        <v>0.04390735830670565</v>
       </c>
       <c r="J90" t="n">
-        <v>47664</v>
+        <v>84075</v>
       </c>
       <c r="K90" t="n">
-        <v>24564</v>
+        <v>130</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>795568</v>
+        <v>771981</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.03055386078154773</v>
+        <v>-0.157670136816504</v>
       </c>
       <c r="E91" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>645619</v>
+        <v>514576</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -11790,35 +11864,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.2546620907310096</v>
+        <v>-0.3794015878701483</v>
       </c>
       <c r="J91" t="n">
-        <v>73857</v>
+        <v>47664</v>
       </c>
       <c r="K91" t="n">
-        <v>45</v>
+        <v>24564</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>813381</v>
+        <v>795568</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.02239029221889267</v>
+        <v>0.03055386078154773</v>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F92" t="n">
-        <v>669130</v>
+        <v>645619</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -11827,35 +11901,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.03641621451661119</v>
+        <v>0.2546620907310096</v>
       </c>
       <c r="J92" t="n">
-        <v>75798</v>
+        <v>73857</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>837712</v>
+        <v>813381</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.02991341081239911</v>
+        <v>0.02239029221889267</v>
       </c>
       <c r="E93" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
-        <v>757865</v>
+        <v>669130</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -11864,10 +11938,10 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.1326124968242345</v>
+        <v>0.03641621451661119</v>
       </c>
       <c r="J93" t="n">
-        <v>77986</v>
+        <v>75798</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -11876,23 +11950,23 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>854381</v>
+        <v>837712</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.01989824665278759</v>
+        <v>0.02991341081239911</v>
       </c>
       <c r="E94" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F94" t="n">
-        <v>768568</v>
+        <v>757865</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -11901,10 +11975,10 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.01412256800353625</v>
+        <v>0.1326124968242345</v>
       </c>
       <c r="J94" t="n">
-        <v>79060</v>
+        <v>77986</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -11913,23 +11987,23 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>878954</v>
+        <v>854381</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.02876117329388177</v>
+        <v>0.01989824665278759</v>
       </c>
       <c r="E95" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F95" t="n">
-        <v>794286</v>
+        <v>768568</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -11938,10 +12012,10 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.03346223105827981</v>
+        <v>0.01412256800353625</v>
       </c>
       <c r="J95" t="n">
-        <v>82273</v>
+        <v>79060</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -11950,59 +12024,96 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>878954</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.02876117329388177</v>
+      </c>
+      <c r="E96" t="n">
+        <v>4</v>
+      </c>
+      <c r="F96" t="n">
+        <v>794286</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.03346223105827981</v>
+      </c>
+      <c r="J96" t="n">
+        <v>82273</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>918791</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.04532319097472678</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>10</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>830324</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>2839</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.0489458457029332</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>84310</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>146810</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>315748</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>2839</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>36646</v>
       </c>
     </row>
@@ -12031,7 +12142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -14747,7 +14858,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -15067,20 +15178,20 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>7612</v>
+        <v>8250</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.07733333333333334</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -15095,16 +15206,16 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>583</v>
+        <v>675</v>
       </c>
       <c r="K82" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -15114,10 +15225,10 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>-0.07733333333333334</v>
       </c>
       <c r="E83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -15132,10 +15243,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="K83" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="84">
@@ -15178,7 +15289,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -15191,7 +15302,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -15206,16 +15317,16 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>668</v>
+        <v>580</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -15228,7 +15339,7 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -15243,7 +15354,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -15252,20 +15363,20 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>7485</v>
+        <v>7612</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.01668418286915397</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -15280,7 +15391,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -15289,7 +15400,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -15299,10 +15410,10 @@
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>-0.01668418286915397</v>
       </c>
       <c r="E88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -15317,7 +15428,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -15326,20 +15437,20 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>8250</v>
+        <v>7485</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.1022044088176353</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -15354,7 +15465,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -15363,20 +15474,20 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>7612</v>
+        <v>8250</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.07733333333333334</v>
+        <v>0.1022044088176353</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -15391,16 +15502,16 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>583</v>
+        <v>675</v>
       </c>
       <c r="K90" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -15410,10 +15521,10 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.07733333333333334</v>
       </c>
       <c r="E91" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -15428,16 +15539,16 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>666</v>
+        <v>583</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -15450,7 +15561,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -15465,7 +15576,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -15474,7 +15585,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -15487,7 +15598,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -15502,7 +15613,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -15511,20 +15622,20 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>7485</v>
+        <v>7612</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.01668418286915397</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -15539,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -15548,7 +15659,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -15558,10 +15669,10 @@
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0</v>
+        <v>-0.01668418286915397</v>
       </c>
       <c r="E95" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -15576,7 +15687,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -15585,59 +15696,96 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>7485</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>4</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>674</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>8250</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.1022044088176353</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>10</v>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
         <v>675</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>638</v>
       </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>92</v>
       </c>
     </row>
@@ -15653,7 +15801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -18369,7 +18517,7 @@
         <v>0.1652209684168718</v>
       </c>
       <c r="E73" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F73" t="n">
         <v>65216</v>
@@ -18689,60 +18837,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>108314</v>
+        <v>164288</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.2317774641294249</v>
+        <v>0.1652209684168718</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>15829</v>
+        <v>65216</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>81414</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.7236316019205588</v>
+        <v>1.560104757747709</v>
       </c>
       <c r="J82" t="n">
-        <v>6741</v>
+        <v>11467</v>
       </c>
       <c r="K82" t="n">
-        <v>2829</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>118600</v>
+        <v>108314</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.09496463984341821</v>
+        <v>-0.3407065640825867</v>
       </c>
       <c r="E83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>35345</v>
+        <v>15829</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -18751,13 +18899,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>1.232926906311201</v>
+        <v>-0.8920480120030008</v>
       </c>
       <c r="J83" t="n">
-        <v>6650</v>
+        <v>6741</v>
       </c>
       <c r="K83" t="n">
-        <v>3181</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="84">
@@ -18773,7 +18921,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.09496463984341821</v>
       </c>
       <c r="E84" t="n">
         <v>10</v>
@@ -18788,7 +18936,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>1.232926906311201</v>
       </c>
       <c r="J84" t="n">
         <v>6650</v>
@@ -18800,23 +18948,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>122470</v>
+        <v>118600</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.03263069139966273</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F85" t="n">
-        <v>41498</v>
+        <v>35345</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -18825,35 +18973,35 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1740840288583958</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>9878</v>
+        <v>6650</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>3181</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>127157</v>
+        <v>122470</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.03827059688086878</v>
+        <v>0.03263069139966273</v>
       </c>
       <c r="E86" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F86" t="n">
-        <v>51337</v>
+        <v>41498</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -18862,10 +19010,10 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.2370957636512603</v>
+        <v>0.1740840288583958</v>
       </c>
       <c r="J86" t="n">
-        <v>10122</v>
+        <v>9878</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -18874,23 +19022,23 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>125374</v>
+        <v>127157</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.01402203575107937</v>
+        <v>0.03827059688086878</v>
       </c>
       <c r="E87" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F87" t="n">
-        <v>56822</v>
+        <v>51337</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -18899,10 +19047,10 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.1068430177065275</v>
+        <v>0.2370957636512603</v>
       </c>
       <c r="J87" t="n">
-        <v>10331</v>
+        <v>10122</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -18911,20 +19059,20 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>140704</v>
+        <v>125374</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.1222741557260676</v>
+        <v>-0.01402203575107937</v>
       </c>
       <c r="E88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F88" t="n">
         <v>56822</v>
@@ -18936,10 +19084,10 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>0.1068430177065275</v>
       </c>
       <c r="J88" t="n">
-        <v>10714</v>
+        <v>10331</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -18948,35 +19096,35 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>141284</v>
+        <v>140704</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.004122128724130088</v>
+        <v>0.1222741557260676</v>
       </c>
       <c r="E89" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F89" t="n">
-        <v>54804</v>
+        <v>56822</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>79817</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>1.369170391749674</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>11081</v>
+        <v>10714</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -18985,60 +19133,60 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>108314</v>
+        <v>141284</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.2333597576512556</v>
+        <v>0.004122128724130088</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F90" t="n">
-        <v>15829</v>
+        <v>54804</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>79817</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.8824180477042958</v>
+        <v>1.369170391749674</v>
       </c>
       <c r="J90" t="n">
-        <v>6741</v>
+        <v>11081</v>
       </c>
       <c r="K90" t="n">
-        <v>2829</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>118600</v>
+        <v>108314</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.09496463984341821</v>
+        <v>-0.2333597576512556</v>
       </c>
       <c r="E91" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>35345</v>
+        <v>15829</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -19047,35 +19195,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>1.232926906311201</v>
+        <v>-0.8824180477042958</v>
       </c>
       <c r="J91" t="n">
-        <v>6394</v>
+        <v>6741</v>
       </c>
       <c r="K91" t="n">
-        <v>3232</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>122822</v>
+        <v>118600</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.03559865092748735</v>
+        <v>0.09496463984341821</v>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F92" t="n">
-        <v>41498</v>
+        <v>35345</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -19084,35 +19232,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.1740840288583958</v>
+        <v>1.232926906311201</v>
       </c>
       <c r="J92" t="n">
-        <v>9899</v>
+        <v>6394</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>3232</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>127169</v>
+        <v>122822</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.03539268209278468</v>
+        <v>0.03559865092748735</v>
       </c>
       <c r="E93" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
-        <v>54148</v>
+        <v>41498</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -19121,10 +19269,10 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.3048339679020676</v>
+        <v>0.1740840288583958</v>
       </c>
       <c r="J93" t="n">
-        <v>10145</v>
+        <v>9899</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -19133,23 +19281,23 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>128119</v>
+        <v>127169</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.007470374069152073</v>
+        <v>0.03539268209278468</v>
       </c>
       <c r="E94" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F94" t="n">
-        <v>56822</v>
+        <v>54148</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -19158,10 +19306,10 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.04938317204698234</v>
+        <v>0.3048339679020676</v>
       </c>
       <c r="J94" t="n">
-        <v>10390</v>
+        <v>10145</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -19170,20 +19318,20 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>140704</v>
+        <v>128119</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.0982289902356403</v>
+        <v>0.007470374069152073</v>
       </c>
       <c r="E95" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F95" t="n">
         <v>56822</v>
@@ -19195,10 +19343,10 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0</v>
+        <v>0.04938317204698234</v>
       </c>
       <c r="J95" t="n">
-        <v>10740</v>
+        <v>10390</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -19207,59 +19355,96 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>140704</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.0982289902356403</v>
+      </c>
+      <c r="E96" t="n">
+        <v>4</v>
+      </c>
+      <c r="F96" t="n">
+        <v>56822</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>10740</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>141284</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.004122128724130088</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>10</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>54995</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>78744</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>1.353648234838619</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>11112</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>32970</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>39166</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>78744</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>4371</v>
       </c>
     </row>
@@ -19275,7 +19460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -21991,7 +22176,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E73" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F73" t="n">
         <v>83286</v>
@@ -22311,23 +22496,23 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>79737</v>
+        <v>97615</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.1819412953596454</v>
+        <v>0.001477362497563378</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>46431</v>
+        <v>83286</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -22336,19 +22521,19 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.3266966357308584</v>
+        <v>0.2077436194895592</v>
       </c>
       <c r="J82" t="n">
-        <v>2434</v>
+        <v>6953</v>
       </c>
       <c r="K82" t="n">
-        <v>3079</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -22358,10 +22543,10 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>-0.1831480817497311</v>
       </c>
       <c r="E83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
         <v>46431</v>
@@ -22373,13 +22558,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>-0.4425113464447806</v>
       </c>
       <c r="J83" t="n">
-        <v>2428</v>
+        <v>2434</v>
       </c>
       <c r="K83" t="n">
-        <v>3395</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="84">
@@ -22422,23 +22607,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>90982</v>
+        <v>79737</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.1410261233806138</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F85" t="n">
-        <v>48866</v>
+        <v>46431</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -22447,32 +22632,32 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.05244341065236588</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>6216</v>
+        <v>2428</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>3395</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>93251</v>
+        <v>90982</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.02493899892286386</v>
+        <v>0.1410261233806138</v>
       </c>
       <c r="E86" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F86" t="n">
         <v>48866</v>
@@ -22484,10 +22669,10 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0</v>
+        <v>0.05244341065236588</v>
       </c>
       <c r="J86" t="n">
-        <v>6266</v>
+        <v>6216</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -22496,23 +22681,23 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>96279</v>
+        <v>93251</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.03247150164609495</v>
+        <v>0.02493899892286386</v>
       </c>
       <c r="E87" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F87" t="n">
-        <v>54278</v>
+        <v>48866</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -22521,10 +22706,10 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.110751852003438</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>6351</v>
+        <v>6266</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -22533,7 +22718,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -22543,13 +22728,13 @@
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>0.03247150164609495</v>
       </c>
       <c r="E88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F88" t="n">
-        <v>58545</v>
+        <v>54278</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -22558,10 +22743,10 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.07861380301411253</v>
+        <v>0.110751852003438</v>
       </c>
       <c r="J88" t="n">
-        <v>6435</v>
+        <v>6351</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -22570,23 +22755,23 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>97615</v>
+        <v>96279</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.01387633855773325</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F89" t="n">
-        <v>83286</v>
+        <v>58545</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -22595,10 +22780,10 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.422598001537279</v>
+        <v>0.07861380301411253</v>
       </c>
       <c r="J89" t="n">
-        <v>6869</v>
+        <v>6435</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -22607,23 +22792,23 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>79737</v>
+        <v>97615</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.1831480817497311</v>
+        <v>0.01387633855773325</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F90" t="n">
-        <v>46431</v>
+        <v>83286</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -22632,32 +22817,32 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.4425113464447806</v>
+        <v>0.422598001537279</v>
       </c>
       <c r="J90" t="n">
-        <v>2434</v>
+        <v>6869</v>
       </c>
       <c r="K90" t="n">
-        <v>3079</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>87942</v>
+        <v>79737</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.1029007863350766</v>
+        <v>-0.1831480817497311</v>
       </c>
       <c r="E91" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
         <v>46431</v>
@@ -22669,35 +22854,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-0.4425113464447806</v>
       </c>
       <c r="J91" t="n">
-        <v>2359</v>
+        <v>2434</v>
       </c>
       <c r="K91" t="n">
-        <v>3430</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>90982</v>
+        <v>87942</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.03456823815696709</v>
+        <v>0.1029007863350766</v>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F92" t="n">
-        <v>48866</v>
+        <v>46431</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -22706,35 +22891,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.05244341065236588</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>6221</v>
+        <v>2359</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>93726</v>
+        <v>90982</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.03015981183091161</v>
+        <v>0.03456823815696709</v>
       </c>
       <c r="E93" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
-        <v>50607</v>
+        <v>48866</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -22743,10 +22928,10 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.03562804403879998</v>
+        <v>0.05244341065236588</v>
       </c>
       <c r="J93" t="n">
-        <v>6271</v>
+        <v>6221</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -22755,20 +22940,20 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>96279</v>
+        <v>93726</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.02723897317713335</v>
+        <v>0.03015981183091161</v>
       </c>
       <c r="E94" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F94" t="n">
         <v>50607</v>
@@ -22780,10 +22965,10 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0</v>
+        <v>0.03562804403879998</v>
       </c>
       <c r="J94" t="n">
-        <v>6357</v>
+        <v>6271</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -22792,7 +22977,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -22802,13 +22987,13 @@
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0</v>
+        <v>0.02723897317713335</v>
       </c>
       <c r="E95" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F95" t="n">
-        <v>58545</v>
+        <v>50607</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -22817,10 +23002,10 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.1568557709407789</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>6447</v>
+        <v>6357</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -22829,59 +23014,96 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>96279</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>4</v>
+      </c>
+      <c r="F96" t="n">
+        <v>58545</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.1568557709407789</v>
+      </c>
+      <c r="J96" t="n">
+        <v>6447</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>97615</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.01387633855773325</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>10</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>83286</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
         <v>0.422598001537279</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>6879</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>17878</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>36855</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>4445</v>
       </c>
     </row>
@@ -22897,7 +23119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -25613,7 +25835,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -25933,20 +26155,20 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>6139</v>
+        <v>6136</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.0004889178617992178</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -25961,16 +26183,16 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>551</v>
+        <v>588</v>
       </c>
       <c r="K82" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -25980,10 +26202,10 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>0.0004889178617992178</v>
       </c>
       <c r="E83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -26001,7 +26223,7 @@
         <v>551</v>
       </c>
       <c r="K83" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84">
@@ -26044,20 +26266,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>6138</v>
+        <v>6139</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>-0.0001628929793125916</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -26072,29 +26294,29 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>583</v>
+        <v>551</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>6158</v>
+        <v>6138</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.003258390355164549</v>
+        <v>-0.0001628929793125916</v>
       </c>
       <c r="E86" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -26118,20 +26340,20 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>6136</v>
+        <v>6158</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.003572588502760637</v>
+        <v>0.003258390355164549</v>
       </c>
       <c r="E87" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -26155,7 +26377,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -26165,10 +26387,10 @@
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>-0.003572588502760637</v>
       </c>
       <c r="E88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -26192,7 +26414,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -26205,7 +26427,7 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -26220,7 +26442,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -26229,20 +26451,20 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>6139</v>
+        <v>6136</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.0004889178617992178</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -26257,16 +26479,16 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>551</v>
+        <v>586</v>
       </c>
       <c r="K90" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -26276,10 +26498,10 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>0.0004889178617992178</v>
       </c>
       <c r="E91" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -26297,26 +26519,26 @@
         <v>551</v>
       </c>
       <c r="K91" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>6138</v>
+        <v>6139</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>-0.0001628929793125916</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -26331,29 +26553,29 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>583</v>
+        <v>551</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>6158</v>
+        <v>6138</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.003258390355164549</v>
+        <v>-0.0001628929793125916</v>
       </c>
       <c r="E93" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -26377,20 +26599,20 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>6136</v>
+        <v>6158</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.003572588502760637</v>
+        <v>0.003258390355164549</v>
       </c>
       <c r="E94" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -26414,7 +26636,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -26424,10 +26646,10 @@
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0</v>
+        <v>-0.003572588502760637</v>
       </c>
       <c r="E95" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -26451,7 +26673,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -26464,46 +26686,83 @@
         <v>0</v>
       </c>
       <c r="E96" t="n">
+        <v>4</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>583</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>6136</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
         <v>10</v>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
         <v>586</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>35</v>
       </c>
     </row>
@@ -26519,7 +26778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -29235,7 +29494,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E73" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29555,20 +29814,20 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>23142</v>
+        <v>27582</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.1528972509974743</v>
+        <v>0.009626999524140707</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -29583,29 +29842,29 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>975</v>
+        <v>1243</v>
       </c>
       <c r="K82" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>58808</v>
+        <v>23142</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>1.541180537550773</v>
+        <v>-0.1609745486186643</v>
       </c>
       <c r="E83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -29620,10 +29879,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>657</v>
+        <v>975</v>
       </c>
       <c r="K83" t="n">
-        <v>534</v>
+        <v>103</v>
       </c>
     </row>
     <row r="84">
@@ -29639,7 +29898,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>1.541180537550773</v>
       </c>
       <c r="E84" t="n">
         <v>10</v>
@@ -29666,20 +29925,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>26385</v>
+        <v>58808</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>-0.5513365528499524</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -29694,16 +29953,16 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>1178</v>
+        <v>657</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>534</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -29713,10 +29972,10 @@
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0</v>
+        <v>-0.5513365528499524</v>
       </c>
       <c r="E86" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -29731,7 +29990,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>1193</v>
+        <v>1178</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -29740,20 +29999,20 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>26336</v>
+        <v>26385</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.001857115785484177</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -29768,29 +30027,29 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>1200</v>
+        <v>1193</v>
       </c>
       <c r="K87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>26385</v>
+        <v>26336</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.001860571081409478</v>
+        <v>-0.001857115785484177</v>
       </c>
       <c r="E88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -29805,29 +30064,29 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>1212</v>
+        <v>1200</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>27319</v>
+        <v>26385</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.03539890089065757</v>
+        <v>0.001860571081409478</v>
       </c>
       <c r="E89" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -29842,7 +30101,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>1233</v>
+        <v>1212</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -29851,20 +30110,20 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>23142</v>
+        <v>27319</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.1528972509974743</v>
+        <v>0.03539890089065757</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -29879,29 +30138,29 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>975</v>
+        <v>1233</v>
       </c>
       <c r="K90" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>58808</v>
+        <v>23142</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>1.541180537550773</v>
+        <v>-0.1528972509974743</v>
       </c>
       <c r="E91" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -29916,29 +30175,29 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>606</v>
+        <v>975</v>
       </c>
       <c r="K91" t="n">
-        <v>550</v>
+        <v>103</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>26385</v>
+        <v>58808</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>-0.5513365528499524</v>
+        <v>1.541180537550773</v>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -29953,16 +30212,16 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>1179</v>
+        <v>606</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -29972,10 +30231,10 @@
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0</v>
+        <v>-0.5513365528499524</v>
       </c>
       <c r="E93" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -29990,7 +30249,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>1194</v>
+        <v>1179</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -29999,20 +30258,20 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>26336</v>
+        <v>26385</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.001857115785484177</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -30027,7 +30286,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>1204</v>
+        <v>1194</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -30036,20 +30295,20 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>26385</v>
+        <v>26336</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.001860571081409478</v>
+        <v>-0.001857115785484177</v>
       </c>
       <c r="E95" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -30064,7 +30323,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>1215</v>
+        <v>1204</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -30073,59 +30332,96 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>26385</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.001860571081409478</v>
+      </c>
+      <c r="E96" t="n">
+        <v>4</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1215</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>27319</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.03539890089065757</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>10</v>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
         <v>1233</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>4177</v>
       </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>258</v>
       </c>
     </row>
@@ -30141,7 +30437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -30785,7 +31081,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -30846,7 +31142,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -30859,7 +31155,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -30874,7 +31170,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -30883,7 +31179,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -30896,7 +31192,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -30918,24 +31214,61 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>11103</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>289</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="4" t="n">
+      <c r="B22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30951,7 +31284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -33667,7 +34000,7 @@
         <v>0.1681714541058927</v>
       </c>
       <c r="E73" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F73" t="n">
         <v>121213</v>
@@ -33987,44 +34320,44 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>125484</v>
+        <v>203909</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.2823293241597035</v>
+        <v>0.1662005501890202</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>77628</v>
+        <v>121213</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>1298</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.1389113820146199</v>
+        <v>0.3589533116659827</v>
       </c>
       <c r="J82" t="n">
-        <v>5023</v>
+        <v>14879</v>
       </c>
       <c r="K82" t="n">
-        <v>3876</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -34034,13 +34367,13 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>-0.3846078397716629</v>
       </c>
       <c r="E83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>84583</v>
+        <v>77628</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -34049,13 +34382,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.08959396094192817</v>
+        <v>-0.3663589391972966</v>
       </c>
       <c r="J83" t="n">
-        <v>6286</v>
+        <v>5023</v>
       </c>
       <c r="K83" t="n">
-        <v>4246</v>
+        <v>3876</v>
       </c>
     </row>
     <row r="84">
@@ -34086,7 +34419,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>0.08959396094192817</v>
       </c>
       <c r="J84" t="n">
         <v>6286</v>
@@ -34098,23 +34431,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>143125</v>
+        <v>125484</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.1405836600682159</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F85" t="n">
-        <v>83216</v>
+        <v>84583</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -34123,35 +34456,35 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>-0.0161616400458721</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>10750</v>
+        <v>6286</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>4246</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>149441</v>
+        <v>143125</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.0441292576419214</v>
+        <v>0.1405836600682159</v>
       </c>
       <c r="E86" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F86" t="n">
-        <v>86719</v>
+        <v>83216</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -34160,10 +34493,10 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.04209527014035763</v>
+        <v>-0.0161616400458721</v>
       </c>
       <c r="J86" t="n">
-        <v>11020</v>
+        <v>10750</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -34172,23 +34505,23 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>150177</v>
+        <v>149441</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.004925020576682437</v>
+        <v>0.0441292576419214</v>
       </c>
       <c r="E87" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F87" t="n">
-        <v>86528</v>
+        <v>86719</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -34197,10 +34530,10 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>-0.002202516172926348</v>
+        <v>0.04209527014035763</v>
       </c>
       <c r="J87" t="n">
-        <v>11272</v>
+        <v>11020</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -34209,23 +34542,23 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>159088</v>
+        <v>150177</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.05933664942035066</v>
+        <v>0.004925020576682437</v>
       </c>
       <c r="E88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F88" t="n">
-        <v>88126</v>
+        <v>86528</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -34234,10 +34567,10 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.01846801035502959</v>
+        <v>-0.002202516172926348</v>
       </c>
       <c r="J88" t="n">
-        <v>12901</v>
+        <v>11272</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -34246,35 +34579,35 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>174849</v>
+        <v>159088</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.09907095444030976</v>
+        <v>0.05933664942035066</v>
       </c>
       <c r="E89" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F89" t="n">
-        <v>105046</v>
+        <v>88126</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>1088</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.2043437804961079</v>
+        <v>0.01846801035502959</v>
       </c>
       <c r="J89" t="n">
-        <v>14383</v>
+        <v>12901</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -34283,60 +34616,60 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>125484</v>
+        <v>174849</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.2823293241597035</v>
+        <v>0.09907095444030976</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F90" t="n">
-        <v>77628</v>
+        <v>105046</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>1088</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.2685849963253999</v>
+        <v>0.2043437804961079</v>
       </c>
       <c r="J90" t="n">
-        <v>5023</v>
+        <v>14383</v>
       </c>
       <c r="K90" t="n">
-        <v>3876</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>36793</v>
+        <v>125484</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>-0.7067913040706385</v>
+        <v>-0.2823293241597035</v>
       </c>
       <c r="E91" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>84583</v>
+        <v>77628</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -34345,35 +34678,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.08959396094192817</v>
+        <v>-0.2685849963253999</v>
       </c>
       <c r="J91" t="n">
-        <v>4963</v>
+        <v>5023</v>
       </c>
       <c r="K91" t="n">
-        <v>5534</v>
+        <v>3876</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>143125</v>
+        <v>36793</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.890006251189085</v>
+        <v>-0.7067913040706385</v>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F92" t="n">
-        <v>83216</v>
+        <v>84583</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -34382,35 +34715,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>-0.0161616400458721</v>
+        <v>0.08959396094192817</v>
       </c>
       <c r="J92" t="n">
-        <v>10755</v>
+        <v>4963</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>5534</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>149787</v>
+        <v>143125</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.04654672489082969</v>
+        <v>2.890006251189085</v>
       </c>
       <c r="E93" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
-        <v>86719</v>
+        <v>83216</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -34419,10 +34752,10 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.04209527014035763</v>
+        <v>-0.0161616400458721</v>
       </c>
       <c r="J93" t="n">
-        <v>11032</v>
+        <v>10755</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -34431,23 +34764,23 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>150177</v>
+        <v>149787</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.002603697250095135</v>
+        <v>0.04654672489082969</v>
       </c>
       <c r="E94" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F94" t="n">
-        <v>78736</v>
+        <v>86719</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -34456,10 +34789,10 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>-0.0920559508296913</v>
+        <v>0.04209527014035763</v>
       </c>
       <c r="J94" t="n">
-        <v>11322</v>
+        <v>11032</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -34468,23 +34801,23 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>159088</v>
+        <v>150177</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.05933664942035066</v>
+        <v>0.002603697250095135</v>
       </c>
       <c r="E95" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F95" t="n">
-        <v>88126</v>
+        <v>78736</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -34493,10 +34826,10 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.1192592968908758</v>
+        <v>-0.0920559508296913</v>
       </c>
       <c r="J95" t="n">
-        <v>12961</v>
+        <v>11322</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -34505,59 +34838,96 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>159088</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.05933664942035066</v>
+      </c>
+      <c r="E96" t="n">
+        <v>4</v>
+      </c>
+      <c r="F96" t="n">
+        <v>88126</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.1192592968908758</v>
+      </c>
+      <c r="J96" t="n">
+        <v>12961</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>174892</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.09934124509705321</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>10</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>105046</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>1088</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.2043437804961079</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>14610</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>49408</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>27418</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>1088</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>9587</v>
       </c>
     </row>
@@ -34573,7 +34943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -37289,7 +37659,7 @@
         <v>0.02667442036863796</v>
       </c>
       <c r="E73" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F73" t="n">
         <v>38311</v>
@@ -37609,60 +37979,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>31413</v>
+        <v>40606</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.2057596520947637</v>
+        <v>0.02667442036863796</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>28900</v>
+        <v>38311</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.2568592661163825</v>
+        <v>-0.01180282342050451</v>
       </c>
       <c r="J82" t="n">
-        <v>1051</v>
+        <v>2632</v>
       </c>
       <c r="K82" t="n">
-        <v>1107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>36790</v>
+        <v>31413</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.1711711711711712</v>
+        <v>-0.2263951140225582</v>
       </c>
       <c r="E83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>33248</v>
+        <v>28900</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -37671,13 +38041,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.1504498269896194</v>
+        <v>-0.2479833463440021</v>
       </c>
       <c r="J83" t="n">
-        <v>1178</v>
+        <v>1051</v>
       </c>
       <c r="K83" t="n">
-        <v>1048</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="84">
@@ -37693,7 +38063,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.1711711711711712</v>
       </c>
       <c r="E84" t="n">
         <v>10</v>
@@ -37708,7 +38078,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>0.1504498269896194</v>
       </c>
       <c r="J84" t="n">
         <v>1178</v>
@@ -37720,23 +38090,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>37455</v>
+        <v>36790</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.01807556401195977</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F85" t="n">
-        <v>25871</v>
+        <v>33248</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -37745,35 +38115,35 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>-0.2218780076997112</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>2245</v>
+        <v>1178</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>37759</v>
+        <v>37455</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.008116406354291816</v>
+        <v>0.01807556401195977</v>
       </c>
       <c r="E86" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F86" t="n">
-        <v>35299</v>
+        <v>25871</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -37782,10 +38152,10 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.3644234857562522</v>
+        <v>-0.2218780076997112</v>
       </c>
       <c r="J86" t="n">
-        <v>2322</v>
+        <v>2245</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -37794,23 +38164,23 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>37867</v>
+        <v>37759</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.002860245239545539</v>
+        <v>0.008116406354291816</v>
       </c>
       <c r="E87" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F87" t="n">
-        <v>37621</v>
+        <v>35299</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -37819,35 +38189,35 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.06578090030879062</v>
+        <v>0.3644234857562522</v>
       </c>
       <c r="J87" t="n">
-        <v>2380</v>
+        <v>2322</v>
       </c>
       <c r="K87" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>38957</v>
+        <v>37867</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.02878495787889191</v>
+        <v>0.002860245239545539</v>
       </c>
       <c r="E88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F88" t="n">
-        <v>38804</v>
+        <v>37621</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -37856,109 +38226,109 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.03144520347678158</v>
+        <v>0.06578090030879062</v>
       </c>
       <c r="J88" t="n">
-        <v>2521</v>
+        <v>2380</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>39551</v>
+        <v>38957</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.01524758066586236</v>
+        <v>0.02878495787889191</v>
       </c>
       <c r="E89" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F89" t="n">
-        <v>38771</v>
+        <v>38804</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.002216266364292341</v>
+        <v>0.03144520347678158</v>
       </c>
       <c r="J89" t="n">
-        <v>2583</v>
+        <v>2521</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>31413</v>
+        <v>39551</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.2057596520947637</v>
+        <v>0.01524758066586236</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F90" t="n">
-        <v>28900</v>
+        <v>38771</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.2568783749035742</v>
+        <v>0.002216266364292341</v>
       </c>
       <c r="J90" t="n">
-        <v>1051</v>
+        <v>2583</v>
       </c>
       <c r="K90" t="n">
-        <v>1107</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>36790</v>
+        <v>31413</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.1711711711711712</v>
+        <v>-0.2057596520947637</v>
       </c>
       <c r="E91" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>33248</v>
+        <v>28900</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -37967,35 +38337,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.1504498269896194</v>
+        <v>-0.2568783749035742</v>
       </c>
       <c r="J91" t="n">
-        <v>2196</v>
+        <v>1051</v>
       </c>
       <c r="K91" t="n">
-        <v>5</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>37455</v>
+        <v>36790</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.01807556401195977</v>
+        <v>0.1711711711711712</v>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F92" t="n">
-        <v>25871</v>
+        <v>33248</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -38004,35 +38374,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>-0.2218780076997112</v>
+        <v>0.1504498269896194</v>
       </c>
       <c r="J92" t="n">
-        <v>2254</v>
+        <v>2196</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>37759</v>
+        <v>37455</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.008116406354291816</v>
+        <v>0.01807556401195977</v>
       </c>
       <c r="E93" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
-        <v>35299</v>
+        <v>25871</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -38041,10 +38411,10 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.3644234857562522</v>
+        <v>-0.2218780076997112</v>
       </c>
       <c r="J93" t="n">
-        <v>2324</v>
+        <v>2254</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -38053,23 +38423,23 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>38247</v>
+        <v>37759</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.01292407108239095</v>
+        <v>0.008116406354291816</v>
       </c>
       <c r="E94" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F94" t="n">
-        <v>37621</v>
+        <v>35299</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -38078,10 +38448,10 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.06578090030879062</v>
+        <v>0.3644234857562522</v>
       </c>
       <c r="J94" t="n">
-        <v>2395</v>
+        <v>2324</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -38090,23 +38460,23 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>38957</v>
+        <v>38247</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.01856354746777525</v>
+        <v>0.01292407108239095</v>
       </c>
       <c r="E95" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F95" t="n">
-        <v>38804</v>
+        <v>37621</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -38115,10 +38485,10 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.03144520347678158</v>
+        <v>0.06578090030879062</v>
       </c>
       <c r="J95" t="n">
-        <v>2525</v>
+        <v>2395</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -38127,59 +38497,96 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>38957</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.01856354746777525</v>
+      </c>
+      <c r="E96" t="n">
+        <v>4</v>
+      </c>
+      <c r="F96" t="n">
+        <v>38804</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.03144520347678158</v>
+      </c>
+      <c r="J96" t="n">
+        <v>2525</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>39551</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.01524758066586236</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>10</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>38825</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>119</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.003607875476754974</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>2585</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>8138</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>9925</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>119</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>1534</v>
       </c>
     </row>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -4216,7 +4216,7 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>10056</v>
+        <v>10057</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -11510,13 +11510,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>936408</v>
+        <v>939276</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.02784735653178023</v>
+        <v>0.03099541402224715</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -11553,7 +11553,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.1755933311120793</v>
+        <v>-0.1781105873034124</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -4201,7 +4201,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>8739</v>
@@ -7860,7 +7860,7 @@
         <v>0.02224814498574916</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>23472</v>
@@ -11510,16 +11510,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>939276</v>
+        <v>939156</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.03099541402224715</v>
+        <v>0.03086369613561674</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>839541</v>
@@ -11553,7 +11553,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.1781105873034124</v>
+        <v>-0.1780055709594572</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
@@ -15191,7 +15191,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -18850,7 +18850,7 @@
         <v>0.1652209684168718</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>65216</v>
@@ -22509,7 +22509,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>83286</v>
@@ -26168,7 +26168,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -29827,7 +29827,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -31155,7 +31155,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -34333,7 +34333,7 @@
         <v>0.1662005501890202</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>121213</v>
@@ -37992,7 +37992,7 @@
         <v>0.02667442036863796</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>38311</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -11537,7 +11537,7 @@
         <v>85644</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -22527,7 +22527,7 @@
         <v>6953</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -37983,13 +37983,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>40606</v>
+        <v>41687</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.02667442036863796</v>
+        <v>0.05400621981745089</v>
       </c>
       <c r="E82" t="n">
         <v>2</v>
@@ -38026,7 +38026,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.2263951140225582</v>
+        <v>-0.2464557296039533</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -4201,7 +4201,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>8739</v>
@@ -7860,7 +7860,7 @@
         <v>0.02224814498574916</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>23472</v>
@@ -11519,7 +11519,7 @@
         <v>0.03086369613561674</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>839541</v>
@@ -11534,10 +11534,10 @@
         <v>0.0272524317320502</v>
       </c>
       <c r="J82" t="n">
-        <v>85644</v>
+        <v>85656</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -15191,7 +15191,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -18850,7 +18850,7 @@
         <v>0.1652209684168718</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>65216</v>
@@ -22509,7 +22509,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>83286</v>
@@ -26168,7 +26168,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -29827,7 +29827,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -31155,7 +31155,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -34333,7 +34333,7 @@
         <v>0.1662005501890202</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>121213</v>
@@ -34351,7 +34351,7 @@
         <v>14879</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -37992,7 +37992,7 @@
         <v>0.05400621981745089</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>38311</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -11534,7 +11534,7 @@
         <v>0.0272524317320502</v>
       </c>
       <c r="J82" t="n">
-        <v>85656</v>
+        <v>85665</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -22524,10 +22524,10 @@
         <v>0.2077436194895592</v>
       </c>
       <c r="J82" t="n">
-        <v>6953</v>
+        <v>6955</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -34348,10 +34348,10 @@
         <v>0.3589533116659827</v>
       </c>
       <c r="J82" t="n">
-        <v>14879</v>
+        <v>14884</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -4219,7 +4219,7 @@
         <v>10057</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -11537,7 +11537,7 @@
         <v>85665</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -18868,7 +18868,7 @@
         <v>11467</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -22527,7 +22527,7 @@
         <v>6955</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -34351,7 +34351,7 @@
         <v>14884</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -11537,7 +11537,7 @@
         <v>85665</v>
       </c>
       <c r="K82" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83">
@@ -18868,7 +18868,7 @@
         <v>11467</v>
       </c>
       <c r="K82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -22527,7 +22527,7 @@
         <v>6955</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -34351,7 +34351,7 @@
         <v>14884</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -11537,7 +11537,7 @@
         <v>85665</v>
       </c>
       <c r="K82" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83">
@@ -18868,7 +18868,7 @@
         <v>11467</v>
       </c>
       <c r="K82" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="83">
@@ -22527,7 +22527,7 @@
         <v>6955</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -4216,10 +4216,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>10057</v>
+        <v>10173</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -11534,10 +11534,10 @@
         <v>0.0272524317320502</v>
       </c>
       <c r="J82" t="n">
-        <v>85665</v>
+        <v>85694</v>
       </c>
       <c r="K82" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -18865,10 +18865,10 @@
         <v>1.560104757747709</v>
       </c>
       <c r="J82" t="n">
-        <v>11467</v>
+        <v>11497</v>
       </c>
       <c r="K82" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -22527,7 +22527,7 @@
         <v>6955</v>
       </c>
       <c r="K82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
@@ -34351,7 +34351,7 @@
         <v>14884</v>
       </c>
       <c r="K82" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -4216,7 +4216,7 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>10173</v>
+        <v>10184</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>0.0272524317320502</v>
       </c>
       <c r="J82" t="n">
-        <v>85694</v>
+        <v>85695</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -22524,10 +22524,10 @@
         <v>0.2077436194895592</v>
       </c>
       <c r="J82" t="n">
-        <v>6955</v>
+        <v>6965</v>
       </c>
       <c r="K82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -4201,7 +4201,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>8739</v>
@@ -7851,16 +7851,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>85003</v>
+        <v>85550</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.02224814498574916</v>
+        <v>0.02882638028694094</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>23472</v>
@@ -7875,7 +7875,7 @@
         <v>1.908039352900012</v>
       </c>
       <c r="J82" t="n">
-        <v>6763</v>
+        <v>6764</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -7894,7 +7894,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.3546345423102714</v>
+        <v>-0.358760958503799</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
@@ -11519,7 +11519,7 @@
         <v>0.03086369613561674</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>839541</v>
@@ -11537,7 +11537,7 @@
         <v>85695</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -15191,7 +15191,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -18850,7 +18850,7 @@
         <v>0.1652209684168718</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>65216</v>
@@ -22509,7 +22509,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>83286</v>
@@ -26168,7 +26168,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -26183,7 +26183,7 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -29827,7 +29827,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -31155,7 +31155,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -34333,7 +34333,7 @@
         <v>0.1662005501890202</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>121213</v>
@@ -34348,10 +34348,10 @@
         <v>0.3589533116659827</v>
       </c>
       <c r="J82" t="n">
-        <v>14884</v>
+        <v>14901</v>
       </c>
       <c r="K82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -37992,7 +37992,7 @@
         <v>0.05400621981745089</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>38311</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -4201,7 +4201,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>8739</v>
@@ -7860,7 +7860,7 @@
         <v>0.02882638028694094</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>23472</v>
@@ -11519,7 +11519,7 @@
         <v>0.03086369613561674</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>839541</v>
@@ -11534,10 +11534,10 @@
         <v>0.0272524317320502</v>
       </c>
       <c r="J82" t="n">
-        <v>85695</v>
+        <v>85707</v>
       </c>
       <c r="K82" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -15191,7 +15191,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -18850,7 +18850,7 @@
         <v>0.1652209684168718</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>65216</v>
@@ -18868,7 +18868,7 @@
         <v>11497</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -22509,7 +22509,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>83286</v>
@@ -26168,7 +26168,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -29827,7 +29827,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -31155,7 +31155,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -34333,7 +34333,7 @@
         <v>0.1662005501890202</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>121213</v>
@@ -34351,7 +34351,7 @@
         <v>14901</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -37992,7 +37992,7 @@
         <v>0.05400621981745089</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>38311</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -11537,7 +11537,7 @@
         <v>85707</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83">
@@ -18868,7 +18868,7 @@
         <v>11497</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -34351,7 +34351,7 @@
         <v>14901</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -38010,7 +38010,7 @@
         <v>2632</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -4201,7 +4201,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>8739</v>
@@ -4219,7 +4219,7 @@
         <v>10184</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83">
@@ -7860,7 +7860,7 @@
         <v>0.02882638028694094</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>23472</v>
@@ -7878,7 +7878,7 @@
         <v>6764</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -11519,7 +11519,7 @@
         <v>0.03086369613561674</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>839541</v>
@@ -11537,7 +11537,7 @@
         <v>85707</v>
       </c>
       <c r="K82" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83">
@@ -15191,7 +15191,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -18850,7 +18850,7 @@
         <v>0.1652209684168718</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>65216</v>
@@ -18868,7 +18868,7 @@
         <v>11497</v>
       </c>
       <c r="K82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -22509,7 +22509,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>83286</v>
@@ -22527,7 +22527,7 @@
         <v>6965</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -26168,7 +26168,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -29827,7 +29827,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -31155,7 +31155,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -34333,7 +34333,7 @@
         <v>0.1662005501890202</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>121213</v>
@@ -34351,7 +34351,7 @@
         <v>14901</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -37992,7 +37992,7 @@
         <v>0.05400621981745089</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>38311</v>
@@ -38010,7 +38010,7 @@
         <v>2632</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -4216,10 +4216,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>10184</v>
+        <v>10209</v>
       </c>
       <c r="K82" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -11534,10 +11534,10 @@
         <v>0.0272524317320502</v>
       </c>
       <c r="J82" t="n">
-        <v>85707</v>
+        <v>85742</v>
       </c>
       <c r="K82" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -18865,10 +18865,10 @@
         <v>1.560104757747709</v>
       </c>
       <c r="J82" t="n">
-        <v>11497</v>
+        <v>11508</v>
       </c>
       <c r="K82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -22527,7 +22527,7 @@
         <v>6965</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -34351,7 +34351,7 @@
         <v>14901</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -4201,7 +4201,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>8739</v>
@@ -4219,7 +4219,7 @@
         <v>10209</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -7860,7 +7860,7 @@
         <v>0.02882638028694094</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>23472</v>
@@ -11519,7 +11519,7 @@
         <v>0.03086369613561674</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>839541</v>
@@ -11534,10 +11534,10 @@
         <v>0.0272524317320502</v>
       </c>
       <c r="J82" t="n">
-        <v>85742</v>
+        <v>85752</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -15191,7 +15191,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -18850,7 +18850,7 @@
         <v>0.1652209684168718</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>65216</v>
@@ -18868,7 +18868,7 @@
         <v>11508</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -22509,7 +22509,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>83286</v>
@@ -26168,7 +26168,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -29827,7 +29827,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -31155,7 +31155,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -34333,7 +34333,7 @@
         <v>0.1662005501890202</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>121213</v>
@@ -37992,7 +37992,7 @@
         <v>0.05400621981745089</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>38311</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -4201,7 +4201,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>8739</v>
@@ -7860,7 +7860,7 @@
         <v>0.02882638028694094</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>23472</v>
@@ -11519,7 +11519,7 @@
         <v>0.03086369613561674</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>839541</v>
@@ -11534,7 +11534,7 @@
         <v>0.0272524317320502</v>
       </c>
       <c r="J82" t="n">
-        <v>85752</v>
+        <v>85768</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -15191,7 +15191,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -18850,7 +18850,7 @@
         <v>0.1652209684168718</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>65216</v>
@@ -22509,7 +22509,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>83286</v>
@@ -22527,7 +22527,7 @@
         <v>6965</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -26168,7 +26168,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -29827,7 +29827,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -31155,7 +31155,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -34333,7 +34333,7 @@
         <v>0.1662005501890202</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>121213</v>
@@ -37992,7 +37992,7 @@
         <v>0.05400621981745089</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>38311</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -4201,7 +4201,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>8739</v>
@@ -7860,7 +7860,7 @@
         <v>0.02882638028694094</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>23472</v>
@@ -11519,7 +11519,7 @@
         <v>0.03086369613561674</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>839541</v>
@@ -11534,7 +11534,7 @@
         <v>0.0272524317320502</v>
       </c>
       <c r="J82" t="n">
-        <v>85768</v>
+        <v>85772</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -15191,7 +15191,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -18850,7 +18850,7 @@
         <v>0.1652209684168718</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>65216</v>
@@ -22509,7 +22509,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>83286</v>
@@ -22527,7 +22527,7 @@
         <v>6965</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -26168,7 +26168,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -29827,7 +29827,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -29842,7 +29842,7 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -31155,7 +31155,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -34333,7 +34333,7 @@
         <v>0.1662005501890202</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>121213</v>
@@ -34348,10 +34348,10 @@
         <v>0.3589533116659827</v>
       </c>
       <c r="J82" t="n">
-        <v>14901</v>
+        <v>14908</v>
       </c>
       <c r="K82" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -37992,7 +37992,7 @@
         <v>0.05400621981745089</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>38311</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -4210,7 +4210,7 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>0</v>
@@ -7869,10 +7869,10 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>47173</v>
+        <v>47991</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>1.908039352900012</v>
+        <v>1.941711604165809</v>
       </c>
       <c r="J82" t="n">
         <v>6764</v>
@@ -11510,34 +11510,34 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>939156</v>
+        <v>939441</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.03086369613561674</v>
+        <v>0.03117652611636397</v>
       </c>
       <c r="E82" t="n">
         <v>12</v>
       </c>
       <c r="F82" t="n">
-        <v>839541</v>
+        <v>841498</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>4804</v>
+        <v>4814</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.0272524317320502</v>
+        <v>0.02964553589352086</v>
       </c>
       <c r="J82" t="n">
-        <v>85772</v>
+        <v>85779</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -11553,7 +11553,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.1780055709594572</v>
+        <v>-0.1782549409702153</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
@@ -11568,7 +11568,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>-0.3905619148570786</v>
+        <v>-0.3919783720424619</v>
       </c>
       <c r="J83" t="n">
         <v>47664</v>
@@ -34342,10 +34342,10 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>1298</v>
+        <v>2484</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.3589533116659827</v>
+        <v>0.372109017093543</v>
       </c>
       <c r="J82" t="n">
         <v>14908</v>
@@ -34382,7 +34382,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>-0.3663589391972966</v>
+        <v>-0.3724342546706872</v>
       </c>
       <c r="J83" t="n">
         <v>5023</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -11537,7 +11537,7 @@
         <v>85779</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -29845,7 +29845,7 @@
         <v>1245</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -38010,7 +38010,7 @@
         <v>2632</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -11537,7 +11537,7 @@
         <v>85779</v>
       </c>
       <c r="K82" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -4201,7 +4201,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>8739</v>
@@ -4216,10 +4216,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>10209</v>
+        <v>10212</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -7860,7 +7860,7 @@
         <v>0.02882638028694094</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>23472</v>
@@ -11519,7 +11519,7 @@
         <v>0.03117652611636397</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>841498</v>
@@ -11534,10 +11534,10 @@
         <v>0.02964553589352086</v>
       </c>
       <c r="J82" t="n">
-        <v>85779</v>
+        <v>85792</v>
       </c>
       <c r="K82" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -15191,7 +15191,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -18850,7 +18850,7 @@
         <v>0.1652209684168718</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>65216</v>
@@ -22509,7 +22509,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>83286</v>
@@ -22524,10 +22524,10 @@
         <v>0.2077436194895592</v>
       </c>
       <c r="J82" t="n">
-        <v>6965</v>
+        <v>6971</v>
       </c>
       <c r="K82" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -26168,7 +26168,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -29827,7 +29827,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -29842,10 +29842,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -31155,7 +31155,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -34333,7 +34333,7 @@
         <v>0.1662005501890202</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>121213</v>
@@ -37992,7 +37992,7 @@
         <v>0.05400621981745089</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" t="n">
         <v>38311</v>
@@ -38007,10 +38007,10 @@
         <v>-0.01180282342050451</v>
       </c>
       <c r="J82" t="n">
-        <v>2632</v>
+        <v>2636</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -4201,7 +4201,7 @@
         <v>0.1426609214636323</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F82" t="n">
         <v>8739</v>
@@ -7860,7 +7860,7 @@
         <v>0.02882638028694094</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F82" t="n">
         <v>23472</v>
@@ -11519,7 +11519,7 @@
         <v>0.03117652611636397</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F82" t="n">
         <v>841498</v>
@@ -15191,7 +15191,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -18850,7 +18850,7 @@
         <v>0.1652209684168718</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F82" t="n">
         <v>65216</v>
@@ -22509,7 +22509,7 @@
         <v>0.001477362497563378</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F82" t="n">
         <v>83286</v>
@@ -26168,7 +26168,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -29827,7 +29827,7 @@
         <v>0.009626999524140707</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -31155,7 +31155,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -34333,7 +34333,7 @@
         <v>0.1662005501890202</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F82" t="n">
         <v>121213</v>
@@ -37992,7 +37992,7 @@
         <v>0.05400621981745089</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F82" t="n">
         <v>38311</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -11534,7 +11534,7 @@
         <v>0.02964553589352086</v>
       </c>
       <c r="J82" t="n">
-        <v>85792</v>
+        <v>85791</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
